--- a/NFL_Edge_Model.xlsx
+++ b/NFL_Edge_Model.xlsx
@@ -715,7 +715,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot of the live model, generated 2026-09-15T16:03:30+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
+          <t>Snapshot of the live model, generated 2026-09-15T20:06:02+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
         </is>
       </c>
     </row>
@@ -3635,7 +3635,7 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T16:03:30+00:00</t>
+          <t>2026-09-15T20:06:02+00:00</t>
         </is>
       </c>
     </row>
@@ -3852,10 +3852,10 @@
         <v>0.75</v>
       </c>
       <c r="L6" s="16" t="n">
-        <v>25.3</v>
+        <v>25.1</v>
       </c>
       <c r="M6" s="16" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="N6" s="5" t="inlineStr">
         <is>
@@ -4014,10 +4014,10 @@
         <v>0.75</v>
       </c>
       <c r="L9" s="11" t="n">
-        <v>20</v>
+        <v>20.5</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>25.4</v>
+        <v>26</v>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>NYJ @ CHI</t>
+          <t>NO @ BAL</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -4097,39 +4097,39 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>NYJ ML</t>
+          <t>NO ML</t>
         </is>
       </c>
       <c r="E11" s="7" t="n">
         <v>320</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>0.2889</v>
+        <v>0.2887</v>
       </c>
       <c r="G11" s="8" t="n">
         <v>0.2381</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>0.05499263989614173</v>
+        <v>0.05499240188638405</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0.2643326039387308</v>
+        <v>0.263457330415755</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>-1.94</v>
+        <v>-1.93</v>
       </c>
       <c r="K11" s="10" t="n">
         <v>0.75</v>
       </c>
       <c r="L11" s="11" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>27.1</v>
+        <v>27</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>NO @ BAL</t>
+          <t>NYJ @ CHI</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -4151,39 +4151,39 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>NO ML</t>
+          <t>NYJ ML</t>
         </is>
       </c>
       <c r="E12" s="12" t="n">
         <v>320</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.2887</v>
+        <v>0.2881</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>0.2381</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>0.05499240188638405</v>
+        <v>0.05499164067675896</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>0.263457330415755</v>
+        <v>0.2608315098468272</v>
       </c>
       <c r="J12" s="14" t="n">
-        <v>-1.93</v>
+        <v>-1.89</v>
       </c>
       <c r="K12" s="15" t="n">
         <v>0.75</v>
       </c>
       <c r="L12" s="16" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="M12" s="16" t="n">
-        <v>27</v>
+        <v>27.1</v>
       </c>
       <c r="N12" s="5" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -4212,19 +4212,19 @@
         <v>320</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0.2836</v>
+        <v>0.2832</v>
       </c>
       <c r="G13" s="8" t="n">
         <v>0.2381</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>0.05498289397347922</v>
+        <v>0.05498176984912592</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.2411378555798687</v>
+        <v>0.2393873085339169</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>-2.62</v>
+        <v>-2.59</v>
       </c>
       <c r="K13" s="10" t="n">
         <v>0.75</v>
@@ -4338,10 +4338,10 @@
         <v>0.75</v>
       </c>
       <c r="L15" s="11" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
@@ -4536,28 +4536,28 @@
         <v>-110</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>0.5873</v>
+        <v>0.5945</v>
       </c>
       <c r="G19" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>0.05480801870864256</v>
+        <v>0.05488619650201235</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0.1746000000000001</v>
+        <v>0.1890000000000001</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>-3.49</v>
+        <v>-3.83</v>
       </c>
       <c r="K19" s="10" t="n">
         <v>0.75</v>
       </c>
       <c r="L19" s="11" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="M19" s="11" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>NYJ @ CHI</t>
+          <t>NO @ BAL</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -5146,23 +5146,23 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>NYJ ML</t>
+          <t>NO ML</t>
         </is>
       </c>
       <c r="E11" s="7" t="n">
         <v>320</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>0.2889</v>
+        <v>0.2887</v>
       </c>
       <c r="G11" s="8" t="n">
         <v>0.2381</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>0.05499263989614173</v>
+        <v>0.05499240188638405</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0.2116516219999999</v>
+        <v>0.2108184260000002</v>
       </c>
       <c r="J11" s="10" t="n">
         <v>0.75</v>
@@ -5177,7 +5177,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>NO @ BAL</t>
+          <t>NYJ @ CHI</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -5187,23 +5187,23 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>NO ML</t>
+          <t>NYJ ML</t>
         </is>
       </c>
       <c r="E12" s="12" t="n">
         <v>320</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.2887</v>
+        <v>0.2881</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>0.2381</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>0.05499240188638405</v>
+        <v>0.05499164067675896</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>0.2108184260000002</v>
+        <v>0.2083188380000001</v>
       </c>
       <c r="J12" s="15" t="n">
         <v>0.75</v>
@@ -5235,16 +5235,16 @@
         <v>320</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0.2836</v>
+        <v>0.2832</v>
       </c>
       <c r="G13" s="8" t="n">
         <v>0.2381</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>0.05498289397347922</v>
+        <v>0.05498176984912592</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.1895910400000002</v>
+        <v>0.1879244800000001</v>
       </c>
       <c r="J13" s="10" t="n">
         <v>0.75</v>
@@ -5481,16 +5481,16 @@
         <v>-110</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>0.5873</v>
+        <v>0.5945</v>
       </c>
       <c r="G19" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>0.05480801870864256</v>
+        <v>0.05488619650201235</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0.121209090909091</v>
+        <v>0.1349545454545455</v>
       </c>
       <c r="J19" s="10" t="n">
         <v>0.75</v>
@@ -5849,33 +5849,33 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>NYJ @ DET</t>
+          <t>PHI @ TEN</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>NYJ +9.5</t>
+          <t>Over 39.5</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5823</v>
+        <v>0.5825</v>
       </c>
       <c r="G28" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H28" s="13" t="n">
-        <v>0.05472403634105155</v>
+        <v>0.05472801145277018</v>
       </c>
       <c r="I28" s="13" t="n">
-        <v>0.1116636363636365</v>
+        <v>0.1120454545454546</v>
       </c>
       <c r="J28" s="15" t="n">
         <v>0.75</v>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>NYG @ LAR</t>
+          <t>NYJ @ DET</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -5904,23 +5904,23 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>NYG +7</t>
+          <t>NYJ +9.5</t>
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>0.5683</v>
+        <v>0.5817</v>
       </c>
       <c r="G29" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.5238</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>0.05469334768692589</v>
+        <v>0.05471175994430898</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0.1036558995238096</v>
+        <v>0.110518181818182</v>
       </c>
       <c r="J29" s="10" t="n">
         <v>0.75</v>
@@ -5939,7 +5939,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>PHI @ TEN</t>
+          <t>NYG @ LAR</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -5949,23 +5949,23 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>TEN +7</t>
+          <t>NYG +7</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.5805</v>
+        <v>0.5683</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5122</v>
       </c>
       <c r="H30" s="13" t="n">
-        <v>0.05468554925400725</v>
+        <v>0.05469334768692589</v>
       </c>
       <c r="I30" s="13" t="n">
-        <v>0.1024587590909092</v>
+        <v>0.1036558995238096</v>
       </c>
       <c r="J30" s="15" t="n">
         <v>0.75</v>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>CLE @ TB</t>
+          <t>PHI @ TEN</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -5994,23 +5994,23 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>CLE +8.5</t>
+          <t>TEN +7</t>
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>0.5743</v>
+        <v>0.5805</v>
       </c>
       <c r="G31" s="8" t="n">
-        <v>0.5192</v>
+        <v>0.5238</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>0.05465651023616758</v>
+        <v>0.05468554925400725</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0.1060592592592593</v>
+        <v>0.1024587590909092</v>
       </c>
       <c r="J31" s="10" t="n">
         <v>0.75</v>
@@ -6029,40 +6029,40 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>SEA @ WSH</t>
+          <t>CLE @ TB</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>WSH ML</t>
+          <t>CLE +8.5</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>154</v>
+        <v>-108</v>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.4372</v>
+        <v>0.5743</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>0.3937</v>
+        <v>0.5192</v>
       </c>
       <c r="H32" s="13" t="n">
-        <v>0.05465126659550069</v>
+        <v>0.05465651023616758</v>
       </c>
       <c r="I32" s="13" t="n">
-        <v>0.1094936079999999</v>
+        <v>0.1060592592592593</v>
       </c>
       <c r="J32" s="15" t="n">
         <v>0.75</v>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>outside the top 6 plays for this week</t>
+          <t>correlated with a stronger play on the same game</t>
         </is>
       </c>
     </row>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>GB @ NYJ</t>
+          <t>SEA @ WSH</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -6084,23 +6084,23 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>NYJ ML</t>
+          <t>WSH ML</t>
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>0.4109</v>
+        <v>0.4372</v>
       </c>
       <c r="G33" s="8" t="n">
-        <v>0.3704</v>
+        <v>0.3937</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>0.05462966439779703</v>
+        <v>0.05465126659550069</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0.1084560730000001</v>
+        <v>0.1094936079999999</v>
       </c>
       <c r="J33" s="10" t="n">
         <v>0.75</v>
@@ -6119,40 +6119,40 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>PHI @ TEN</t>
+          <t>GB @ NYJ</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Over 39.5</t>
+          <t>NYJ ML</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>-110</v>
+        <v>170</v>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.5776</v>
+        <v>0.4102</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.3704</v>
       </c>
       <c r="H34" s="13" t="n">
-        <v>0.05461197663388877</v>
+        <v>0.05460225861278938</v>
       </c>
       <c r="I34" s="13" t="n">
-        <v>0.1026909090909092</v>
+        <v>0.1065828940000002</v>
       </c>
       <c r="J34" s="15" t="n">
         <v>0.75</v>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>correlated with a stronger play on the same game</t>
+          <t>outside the top 6 plays for this week</t>
         </is>
       </c>
     </row>
@@ -6254,40 +6254,40 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>NYJ @ CHI</t>
+          <t>DET @ BUF</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>NYJ +8.5</t>
+          <t>Under 53.5</t>
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>0.5745</v>
+        <v>0.5616</v>
       </c>
       <c r="G37" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5122</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>0.05451428189255149</v>
+        <v>0.05449631707931886</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0.09677272727272723</v>
+        <v>0.0964571428571428</v>
       </c>
       <c r="J37" s="10" t="n">
         <v>0.75</v>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>correlated with a stronger play on the same game</t>
+          <t>outside the top 6 plays for this week</t>
         </is>
       </c>
     </row>
@@ -6299,40 +6299,40 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>DET @ BUF</t>
+          <t>NYJ @ CHI</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Under 53.5</t>
+          <t>NYJ +8.5</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.5616</v>
+        <v>0.5737</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.5238</v>
       </c>
       <c r="H38" s="13" t="n">
-        <v>0.05449631707931886</v>
+        <v>0.05448531979150142</v>
       </c>
       <c r="I38" s="13" t="n">
-        <v>0.0964571428571428</v>
+        <v>0.09524545454545463</v>
       </c>
       <c r="J38" s="15" t="n">
         <v>0.75</v>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>outside the top 6 plays for this week</t>
+          <t>correlated with a stronger play on the same game</t>
         </is>
       </c>
     </row>
@@ -7261,16 +7261,16 @@
         <v>-118</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>0.5691000000000001</v>
+        <v>0.5684</v>
       </c>
       <c r="G59" s="8" t="n">
         <v>0.5413</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>0.05216838033344296</v>
+        <v>0.05202944547306743</v>
       </c>
       <c r="I59" s="8" t="n">
-        <v>0.05138813559322042</v>
+        <v>0.05009491525423737</v>
       </c>
       <c r="J59" s="10" t="n">
         <v>0.75</v>
@@ -7289,7 +7289,7 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>PHI @ CHI</t>
+          <t>MIN @ TB</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
+          <t>Over 44.5</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
@@ -7334,7 +7334,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>DET @ CAR</t>
+          <t>PHI @ CHI</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -7344,30 +7344,30 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="E61" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>0.5455</v>
+        <v>0.548</v>
       </c>
       <c r="G61" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>0.0511213305922864</v>
+        <v>0.05174707951799837</v>
       </c>
       <c r="I61" s="8" t="n">
-        <v>0.04140909090909095</v>
+        <v>0.04618181818181832</v>
       </c>
       <c r="J61" s="10" t="n">
         <v>0.75</v>
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>correlated with a stronger play on the same game</t>
+          <t>outside the top 6 plays for this week</t>
         </is>
       </c>
     </row>
@@ -7379,33 +7379,33 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>SEA @ ARI</t>
+          <t>DET @ CAR</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>ARI +4.5</t>
+          <t>Over 47.5</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.5572</v>
+        <v>0.5455</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.5238</v>
       </c>
       <c r="H62" s="13" t="n">
-        <v>0.0510992134200146</v>
+        <v>0.0511213305922864</v>
       </c>
       <c r="I62" s="13" t="n">
-        <v>0.04172173913043475</v>
+        <v>0.04140909090909095</v>
       </c>
       <c r="J62" s="15" t="n">
         <v>0.75</v>
@@ -7424,7 +7424,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>WSH @ DAL</t>
+          <t>SEA @ ARI</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -7434,23 +7434,23 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>WSH +3.5</t>
+          <t>ARI +4.5</t>
         </is>
       </c>
       <c r="E63" s="7" t="n">
-        <v>-108</v>
+        <v>-115</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>0.5407</v>
+        <v>0.5572</v>
       </c>
       <c r="G63" s="8" t="n">
-        <v>0.5192</v>
+        <v>0.5349</v>
       </c>
       <c r="H63" s="8" t="n">
-        <v>0.05109138169709417</v>
+        <v>0.0510992134200146</v>
       </c>
       <c r="I63" s="8" t="n">
-        <v>0.04134814814814813</v>
+        <v>0.04172173913043475</v>
       </c>
       <c r="J63" s="10" t="n">
         <v>0.75</v>
@@ -7469,7 +7469,7 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>MIN @ CHI</t>
+          <t>WSH @ DAL</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -7479,23 +7479,23 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>MIN +5.5</t>
+          <t>WSH +3.5</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.5446</v>
+        <v>0.5407</v>
       </c>
       <c r="G64" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5192</v>
       </c>
       <c r="H64" s="13" t="n">
-        <v>0.05086881468618579</v>
+        <v>0.05109138169709417</v>
       </c>
       <c r="I64" s="13" t="n">
-        <v>0.039690909090909</v>
+        <v>0.04134814814814813</v>
       </c>
       <c r="J64" s="15" t="n">
         <v>0.75</v>
@@ -7514,7 +7514,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>DET @ CAR</t>
+          <t>MIN @ CHI</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -7524,23 +7524,23 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>CAR +3</t>
+          <t>MIN +5.5</t>
         </is>
       </c>
       <c r="E65" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>0.5436</v>
+        <v>0.5446</v>
       </c>
       <c r="G65" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H65" s="8" t="n">
-        <v>0.05056972123582922</v>
+        <v>0.05086881468618579</v>
       </c>
       <c r="I65" s="8" t="n">
-        <v>0.03509930909090905</v>
+        <v>0.039690909090909</v>
       </c>
       <c r="J65" s="10" t="n">
         <v>0.75</v>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>IND @ KC</t>
+          <t>DET @ CAR</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -7569,23 +7569,23 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>IND +6.5</t>
+          <t>CAR +3</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>100</v>
+        <v>-110</v>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5189</v>
+        <v>0.5436</v>
       </c>
       <c r="G66" s="13" t="n">
-        <v>0.5</v>
+        <v>0.5238</v>
       </c>
       <c r="H66" s="13" t="n">
-        <v>0.05019743882926531</v>
+        <v>0.05056972123582922</v>
       </c>
       <c r="I66" s="13" t="n">
-        <v>0.03780000000000006</v>
+        <v>0.03509930909090905</v>
       </c>
       <c r="J66" s="15" t="n">
         <v>0.75</v>
@@ -7604,7 +7604,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>PIT @ NE</t>
+          <t>IND @ KC</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -7614,28 +7614,32 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>PIT +5.5</t>
+          <t>IND +6.5</t>
         </is>
       </c>
       <c r="E67" s="7" t="n">
-        <v>-110</v>
+        <v>100</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>0.5407</v>
+        <v>0.5189</v>
       </c>
       <c r="G67" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>0.04958073933075705</v>
+        <v>0.05019743882926531</v>
       </c>
       <c r="I67" s="8" t="n">
-        <v>0.03224545454545447</v>
+        <v>0.03780000000000006</v>
       </c>
       <c r="J67" s="10" t="n">
         <v>0.75</v>
       </c>
-      <c r="K67" s="4" t="inlineStr"/>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>correlated with a stronger play on the same game</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -7645,33 +7649,33 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>SEA @ ARI</t>
+          <t>PIT @ NE</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Over 41.5</t>
+          <t>PIT +5.5</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.538</v>
+        <v>0.5407</v>
       </c>
       <c r="G68" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H68" s="13" t="n">
-        <v>0.04847467639497067</v>
+        <v>0.04958073933075705</v>
       </c>
       <c r="I68" s="13" t="n">
-        <v>0.02709090909090928</v>
+        <v>0.03224545454545447</v>
       </c>
       <c r="J68" s="15" t="n">
         <v>0.75</v>
@@ -7686,33 +7690,33 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>DEN @ SF</t>
+          <t>SEA @ ARI</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>SF -2.5</t>
+          <t>Over 41.5</t>
         </is>
       </c>
       <c r="E69" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>0.5371</v>
+        <v>0.538</v>
       </c>
       <c r="G69" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H69" s="8" t="n">
-        <v>0.04806111990959907</v>
+        <v>0.04847467639497067</v>
       </c>
       <c r="I69" s="8" t="n">
-        <v>0.02537272727272732</v>
+        <v>0.02709090909090928</v>
       </c>
       <c r="J69" s="10" t="n">
         <v>0.75</v>
@@ -7727,33 +7731,33 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>DET @ BUF</t>
+          <t>DEN @ SF</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>DET ML</t>
+          <t>SF -2.5</t>
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>170</v>
+        <v>-110</v>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.3814</v>
+        <v>0.5371</v>
       </c>
       <c r="G70" s="13" t="n">
-        <v>0.3704</v>
+        <v>0.5238</v>
       </c>
       <c r="H70" s="13" t="n">
-        <v>0.04788387862675234</v>
+        <v>0.04806111990959907</v>
       </c>
       <c r="I70" s="13" t="n">
-        <v>0.02952091400000014</v>
+        <v>0.02537272727272732</v>
       </c>
       <c r="J70" s="15" t="n">
         <v>0.75</v>
@@ -7768,7 +7772,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>LAR @ DEN</t>
+          <t>DET @ BUF</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -7778,23 +7782,23 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>DEN ML</t>
+          <t>DET ML</t>
         </is>
       </c>
       <c r="E71" s="7" t="n">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>0.4467</v>
+        <v>0.3814</v>
       </c>
       <c r="G71" s="8" t="n">
-        <v>0.4348</v>
+        <v>0.3704</v>
       </c>
       <c r="H71" s="8" t="n">
-        <v>0.04732316015290161</v>
+        <v>0.04788387862675234</v>
       </c>
       <c r="I71" s="8" t="n">
-        <v>0.02716605099999993</v>
+        <v>0.02952091400000014</v>
       </c>
       <c r="J71" s="10" t="n">
         <v>0.75</v>
@@ -7809,7 +7813,7 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>MIN @ TB</t>
+          <t>PIT @ NE</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -7819,23 +7823,23 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Over 44.5</t>
+          <t>Over 42.5</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.5355</v>
+        <v>0.5241</v>
       </c>
       <c r="G72" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5122</v>
       </c>
       <c r="H72" s="13" t="n">
-        <v>0.04726504445816375</v>
+        <v>0.04735373067950441</v>
       </c>
       <c r="I72" s="13" t="n">
-        <v>0.0223181818181819</v>
+        <v>0.02324285714285712</v>
       </c>
       <c r="J72" s="15" t="n">
         <v>0.75</v>
@@ -7855,28 +7859,28 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>DEN +3</t>
+          <t>DEN ML</t>
         </is>
       </c>
       <c r="E73" s="7" t="n">
-        <v>-110</v>
+        <v>130</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>0.5354</v>
+        <v>0.4467</v>
       </c>
       <c r="G73" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.4348</v>
       </c>
       <c r="H73" s="8" t="n">
-        <v>0.04721258219660927</v>
+        <v>0.04732316015290161</v>
       </c>
       <c r="I73" s="8" t="n">
-        <v>0.0205473854545455</v>
+        <v>0.02716605099999993</v>
       </c>
       <c r="J73" s="10" t="n">
         <v>0.75</v>
@@ -7891,33 +7895,33 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>LV @ NO</t>
+          <t>LAR @ DEN</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>LV ML</t>
+          <t>DEN +3</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>154</v>
+        <v>-110</v>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.4034</v>
+        <v>0.5354</v>
       </c>
       <c r="G74" s="13" t="n">
-        <v>0.3937</v>
+        <v>0.5238</v>
       </c>
       <c r="H74" s="13" t="n">
-        <v>0.04661605208768294</v>
+        <v>0.04721258219660927</v>
       </c>
       <c r="I74" s="13" t="n">
-        <v>0.02441920319999988</v>
+        <v>0.0205473854545455</v>
       </c>
       <c r="J74" s="15" t="n">
         <v>0.75</v>
@@ -7932,33 +7936,33 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>LAR @ PHI</t>
+          <t>LV @ NO</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>PHI +1.5</t>
+          <t>LV ML</t>
         </is>
       </c>
       <c r="E75" s="7" t="n">
-        <v>-110</v>
+        <v>154</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>0.5332</v>
+        <v>0.4034</v>
       </c>
       <c r="G75" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.3937</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>0.045972273989346</v>
+        <v>0.04661605208768294</v>
       </c>
       <c r="I75" s="8" t="n">
-        <v>0.01792727272727279</v>
+        <v>0.02441920319999988</v>
       </c>
       <c r="J75" s="10" t="n">
         <v>0.75</v>
@@ -7973,33 +7977,33 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>TEN @ NYG</t>
+          <t>LAR @ PHI</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Over 44.5</t>
+          <t>PHI +1.5</t>
         </is>
       </c>
       <c r="E76" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.533</v>
+        <v>0.5332</v>
       </c>
       <c r="G76" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H76" s="13" t="n">
-        <v>0.04585100338566855</v>
+        <v>0.045972273989346</v>
       </c>
       <c r="I76" s="13" t="n">
-        <v>0.01754545454545475</v>
+        <v>0.01792727272727279</v>
       </c>
       <c r="J76" s="15" t="n">
         <v>0.75</v>
@@ -8014,33 +8018,33 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>NE @ JAX</t>
+          <t>TEN @ NYG</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>JAX ML</t>
+          <t>Over 44.5</t>
         </is>
       </c>
       <c r="E77" s="7" t="n">
-        <v>-118</v>
+        <v>-110</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>0.5501</v>
+        <v>0.533</v>
       </c>
       <c r="G77" s="8" t="n">
-        <v>0.5413</v>
+        <v>0.5238</v>
       </c>
       <c r="H77" s="8" t="n">
-        <v>0.04496010324745763</v>
+        <v>0.04585100338566855</v>
       </c>
       <c r="I77" s="8" t="n">
-        <v>0.01614149135593224</v>
+        <v>0.01754545454545475</v>
       </c>
       <c r="J77" s="10" t="n">
         <v>0.75</v>
@@ -8055,7 +8059,7 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>LAR @ PHI</t>
+          <t>NE @ JAX</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
@@ -8065,23 +8069,23 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>PHI ML</t>
+          <t>JAX ML</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>102</v>
+        <v>-118</v>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.5038</v>
+        <v>0.5501</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>0.495</v>
+        <v>0.5413</v>
       </c>
       <c r="H78" s="13" t="n">
-        <v>0.04492450168407628</v>
+        <v>0.04496010324745763</v>
       </c>
       <c r="I78" s="13" t="n">
-        <v>0.01751691600000002</v>
+        <v>0.01614149135593224</v>
       </c>
       <c r="J78" s="15" t="n">
         <v>0.75</v>
@@ -8096,33 +8100,33 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>NE @ JAX</t>
+          <t>LAR @ PHI</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>JAX -1.5</t>
+          <t>PHI ML</t>
         </is>
       </c>
       <c r="E79" s="7" t="n">
-        <v>-105</v>
+        <v>102</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>0.5195</v>
+        <v>0.5038</v>
       </c>
       <c r="G79" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.495</v>
       </c>
       <c r="H79" s="8" t="n">
-        <v>0.04453322672379493</v>
+        <v>0.04492450168407628</v>
       </c>
       <c r="I79" s="8" t="n">
-        <v>0.01426190476190459</v>
+        <v>0.01751691600000002</v>
       </c>
       <c r="J79" s="10" t="n">
         <v>0.75</v>
@@ -8137,33 +8141,33 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>CIN @ HOU</t>
+          <t>NE @ JAX</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
+          <t>JAX -1.5</t>
         </is>
       </c>
       <c r="E80" s="12" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.5264</v>
+        <v>0.5195</v>
       </c>
       <c r="G80" s="13" t="n">
-        <v>0.5192</v>
+        <v>0.5122</v>
       </c>
       <c r="H80" s="13" t="n">
-        <v>0.04453142292804473</v>
+        <v>0.04453322672379493</v>
       </c>
       <c r="I80" s="13" t="n">
-        <v>0.01380740740740749</v>
+        <v>0.01426190476190459</v>
       </c>
       <c r="J80" s="15" t="n">
         <v>0.75</v>
@@ -8178,33 +8182,33 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>DET @ BUF</t>
+          <t>CIN @ HOU</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>DET +4.5</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="E81" s="7" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>0.5353</v>
+        <v>0.5264</v>
       </c>
       <c r="G81" s="8" t="n">
-        <v>0.5283</v>
+        <v>0.5192</v>
       </c>
       <c r="H81" s="8" t="n">
-        <v>0.04437145591087985</v>
+        <v>0.04453142292804473</v>
       </c>
       <c r="I81" s="8" t="n">
-        <v>0.01324642857142844</v>
+        <v>0.01380740740740749</v>
       </c>
       <c r="J81" s="10" t="n">
         <v>0.75</v>
@@ -8219,33 +8223,33 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>KC @ MIA</t>
+          <t>DET @ BUF</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Over 44.5</t>
+          <t>DET +4.5</t>
         </is>
       </c>
       <c r="E82" s="12" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.5305</v>
+        <v>0.5353</v>
       </c>
       <c r="G82" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5283</v>
       </c>
       <c r="H82" s="13" t="n">
-        <v>0.04420574441993437</v>
+        <v>0.04437145591087985</v>
       </c>
       <c r="I82" s="13" t="n">
-        <v>0.01277272727272716</v>
+        <v>0.01324642857142844</v>
       </c>
       <c r="J82" s="15" t="n">
         <v>0.75</v>
@@ -8301,7 +8305,7 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>ATL @ GB</t>
+          <t>GB @ NYJ</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
@@ -8311,23 +8315,23 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Under 46.5</t>
+          <t>Over 44.5</t>
         </is>
       </c>
       <c r="E84" s="12" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.5279</v>
+        <v>0.5345</v>
       </c>
       <c r="G84" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5283</v>
       </c>
       <c r="H84" s="13" t="n">
-        <v>0.04221995376217121</v>
+        <v>0.04380454755117143</v>
       </c>
       <c r="I84" s="13" t="n">
-        <v>0.007809090909091099</v>
+        <v>0.01173214285714286</v>
       </c>
       <c r="J84" s="15" t="n">
         <v>0.75</v>
@@ -9039,7 +9043,7 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>NE @ JAX</t>
+          <t>KC @ MIA</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
@@ -9049,7 +9053,7 @@
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>Under 45.5</t>
+          <t>Over 44.5</t>
         </is>
       </c>
       <c r="E102" s="12" t="n">
@@ -9531,7 +9535,7 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>IND @ KC</t>
+          <t>NYJ @ DET</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
@@ -9541,7 +9545,7 @@
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
+          <t>Over 45.5</t>
         </is>
       </c>
       <c r="E114" s="12" t="n">
@@ -9572,33 +9576,33 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>NYJ @ DET</t>
+          <t>JAX @ DEN</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Over 45.5</t>
+          <t>JAX ML</t>
         </is>
       </c>
       <c r="E115" s="7" t="n">
-        <v>-110</v>
+        <v>114</v>
       </c>
       <c r="F115" s="8" t="n">
-        <v>0.5153</v>
+        <v>0.4623</v>
       </c>
       <c r="G115" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.4673</v>
       </c>
       <c r="H115" s="8" t="n">
-        <v>0.02779009306515143</v>
+        <v>0.02774498107434066</v>
       </c>
       <c r="I115" s="8" t="n">
-        <v>-0.01624545454545456</v>
+        <v>-0.01058189800000018</v>
       </c>
       <c r="J115" s="10" t="n">
         <v>0.75</v>
@@ -9613,7 +9617,7 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>JAX @ DEN</t>
+          <t>NE @ BUF</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
@@ -9623,23 +9627,23 @@
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>JAX ML</t>
+          <t>NE ML</t>
         </is>
       </c>
       <c r="E116" s="12" t="n">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="F116" s="13" t="n">
-        <v>0.4623</v>
+        <v>0.4186</v>
       </c>
       <c r="G116" s="13" t="n">
-        <v>0.4673</v>
+        <v>0.4237</v>
       </c>
       <c r="H116" s="13" t="n">
-        <v>0.02774498107434066</v>
+        <v>0.0269725755211132</v>
       </c>
       <c r="I116" s="13" t="n">
-        <v>-0.01058189800000018</v>
+        <v>-0.01199748479999978</v>
       </c>
       <c r="J116" s="15" t="n">
         <v>0.75</v>
@@ -9654,33 +9658,33 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>NE @ BUF</t>
+          <t>MIN @ CHI</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>NE ML</t>
+          <t>Over 49.5</t>
         </is>
       </c>
       <c r="E117" s="7" t="n">
-        <v>136</v>
+        <v>-102</v>
       </c>
       <c r="F117" s="8" t="n">
-        <v>0.4186</v>
+        <v>0.4965</v>
       </c>
       <c r="G117" s="8" t="n">
-        <v>0.4237</v>
+        <v>0.505</v>
       </c>
       <c r="H117" s="8" t="n">
-        <v>0.0269725755211132</v>
+        <v>0.02642937776194846</v>
       </c>
       <c r="I117" s="8" t="n">
-        <v>-0.01199748479999978</v>
+        <v>-0.01673529411764707</v>
       </c>
       <c r="J117" s="10" t="n">
         <v>0.75</v>
@@ -9695,33 +9699,33 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>MIN @ CHI</t>
+          <t>JAX @ DEN</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
+          <t>JAX +2.5</t>
         </is>
       </c>
       <c r="E118" s="12" t="n">
-        <v>-102</v>
+        <v>-110</v>
       </c>
       <c r="F118" s="13" t="n">
-        <v>0.4965</v>
+        <v>0.5142</v>
       </c>
       <c r="G118" s="13" t="n">
-        <v>0.505</v>
+        <v>0.5238</v>
       </c>
       <c r="H118" s="13" t="n">
-        <v>0.02642937776194846</v>
+        <v>0.02611887220744774</v>
       </c>
       <c r="I118" s="13" t="n">
-        <v>-0.01673529411764707</v>
+        <v>-0.01834545454545455</v>
       </c>
       <c r="J118" s="15" t="n">
         <v>0.75</v>
@@ -9736,33 +9740,33 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>JAX @ DEN</t>
+          <t>LAC @ BUF</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>JAX +2.5</t>
+          <t>BUF ML</t>
         </is>
       </c>
       <c r="E119" s="7" t="n">
-        <v>-110</v>
+        <v>-162</v>
       </c>
       <c r="F119" s="8" t="n">
-        <v>0.5142</v>
+        <v>0.6091</v>
       </c>
       <c r="G119" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.6183</v>
       </c>
       <c r="H119" s="8" t="n">
-        <v>0.02611887220744774</v>
+        <v>0.02458958803445027</v>
       </c>
       <c r="I119" s="8" t="n">
-        <v>-0.01834545454545455</v>
+        <v>-0.01478409950617283</v>
       </c>
       <c r="J119" s="10" t="n">
         <v>0.75</v>
@@ -9777,33 +9781,33 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>LAC @ BUF</t>
+          <t>MIA @ SF</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>BUF ML</t>
+          <t>Over 45.5</t>
         </is>
       </c>
       <c r="E120" s="12" t="n">
-        <v>-162</v>
+        <v>-108</v>
       </c>
       <c r="F120" s="13" t="n">
-        <v>0.6091</v>
+        <v>0.5087</v>
       </c>
       <c r="G120" s="13" t="n">
-        <v>0.6183</v>
+        <v>0.5192</v>
       </c>
       <c r="H120" s="13" t="n">
-        <v>0.02458958803445027</v>
+        <v>0.02440348150042199</v>
       </c>
       <c r="I120" s="13" t="n">
-        <v>-0.01478409950617283</v>
+        <v>-0.02028148148148134</v>
       </c>
       <c r="J120" s="15" t="n">
         <v>0.75</v>
@@ -9818,33 +9822,33 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>MIA @ SF</t>
+          <t>TEN @ NYG</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Over 45.5</t>
+          <t>NYG -3</t>
         </is>
       </c>
       <c r="E121" s="7" t="n">
-        <v>-108</v>
+        <v>-115</v>
       </c>
       <c r="F121" s="8" t="n">
-        <v>0.5087</v>
+        <v>0.5239</v>
       </c>
       <c r="G121" s="8" t="n">
-        <v>0.5192</v>
+        <v>0.5349</v>
       </c>
       <c r="H121" s="8" t="n">
-        <v>0.02440348150042199</v>
+        <v>0.02393590335844072</v>
       </c>
       <c r="I121" s="8" t="n">
-        <v>-0.02028148148148134</v>
+        <v>-0.01905422478260872</v>
       </c>
       <c r="J121" s="10" t="n">
         <v>0.75</v>
@@ -9859,7 +9863,7 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>TEN @ NYG</t>
+          <t>LAC @ SEA</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
@@ -9869,23 +9873,23 @@
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>NYG -3</t>
+          <t>SEA -3</t>
         </is>
       </c>
       <c r="E122" s="12" t="n">
         <v>-115</v>
       </c>
       <c r="F122" s="13" t="n">
-        <v>0.5239</v>
+        <v>0.5235</v>
       </c>
       <c r="G122" s="13" t="n">
         <v>0.5349</v>
       </c>
       <c r="H122" s="13" t="n">
-        <v>0.02393590335844072</v>
+        <v>0.02329721808064597</v>
       </c>
       <c r="I122" s="13" t="n">
-        <v>-0.01905422478260872</v>
+        <v>-0.01974813260869581</v>
       </c>
       <c r="J122" s="15" t="n">
         <v>0.75</v>
@@ -9900,33 +9904,33 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>LAC @ SEA</t>
+          <t>NO @ BAL</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>SEA -3</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="E123" s="7" t="n">
-        <v>-115</v>
+        <v>-118</v>
       </c>
       <c r="F123" s="8" t="n">
-        <v>0.5235</v>
+        <v>0.5289</v>
       </c>
       <c r="G123" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.5413</v>
       </c>
       <c r="H123" s="8" t="n">
-        <v>0.02329721808064597</v>
+        <v>0.02109070592057211</v>
       </c>
       <c r="I123" s="8" t="n">
-        <v>-0.01974813260869581</v>
+        <v>-0.02287966101694916</v>
       </c>
       <c r="J123" s="10" t="n">
         <v>0.75</v>
@@ -9941,7 +9945,7 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>NO @ BAL</t>
+          <t>GB @ TB</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
@@ -9951,23 +9955,23 @@
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
+          <t>Over 47.5</t>
         </is>
       </c>
       <c r="E124" s="12" t="n">
-        <v>-118</v>
+        <v>-110</v>
       </c>
       <c r="F124" s="13" t="n">
-        <v>0.5289</v>
+        <v>0.5102</v>
       </c>
       <c r="G124" s="13" t="n">
-        <v>0.5413</v>
+        <v>0.5238</v>
       </c>
       <c r="H124" s="13" t="n">
-        <v>0.02109070592057211</v>
+        <v>0.01951326459787421</v>
       </c>
       <c r="I124" s="13" t="n">
-        <v>-0.02287966101694916</v>
+        <v>-0.02598181818181822</v>
       </c>
       <c r="J124" s="15" t="n">
         <v>0.75</v>
@@ -9982,7 +9986,7 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>GB @ TB</t>
+          <t>ATL @ NO</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
@@ -9992,23 +9996,23 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
+          <t>Under 45.5</t>
         </is>
       </c>
       <c r="E125" s="7" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F125" s="8" t="n">
-        <v>0.5102</v>
+        <v>0.4988</v>
       </c>
       <c r="G125" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5122</v>
       </c>
       <c r="H125" s="8" t="n">
-        <v>0.01951326459787421</v>
+        <v>0.01883146564986645</v>
       </c>
       <c r="I125" s="8" t="n">
-        <v>-0.02598181818181822</v>
+        <v>-0.02615238095238093</v>
       </c>
       <c r="J125" s="10" t="n">
         <v>0.75</v>
@@ -10023,33 +10027,33 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>ATL @ NO</t>
+          <t>NE @ BUF</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>Under 45.5</t>
+          <t>NE +3</t>
         </is>
       </c>
       <c r="E126" s="12" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="F126" s="13" t="n">
-        <v>0.4988</v>
+        <v>0.5095</v>
       </c>
       <c r="G126" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.5238</v>
       </c>
       <c r="H126" s="13" t="n">
-        <v>0.01883146564986645</v>
+        <v>0.01827860408321831</v>
       </c>
       <c r="I126" s="13" t="n">
-        <v>-0.02615238095238093</v>
+        <v>-0.02534854090909099</v>
       </c>
       <c r="J126" s="15" t="n">
         <v>0.75</v>
@@ -10064,33 +10068,33 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>NE @ BUF</t>
+          <t>TEN @ NYG</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>NE +3</t>
+          <t>NYG ML</t>
         </is>
       </c>
       <c r="E127" s="7" t="n">
-        <v>-110</v>
+        <v>-166</v>
       </c>
       <c r="F127" s="8" t="n">
-        <v>0.5095</v>
+        <v>0.6108</v>
       </c>
       <c r="G127" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.6241</v>
       </c>
       <c r="H127" s="8" t="n">
-        <v>0.01827860408321831</v>
+        <v>0.01799261307474052</v>
       </c>
       <c r="I127" s="8" t="n">
-        <v>-0.02534854090909099</v>
+        <v>-0.02106545831325304</v>
       </c>
       <c r="J127" s="10" t="n">
         <v>0.75</v>
@@ -10105,33 +10109,33 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>TEN @ NYG</t>
+          <t>SEA @ WSH</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>NYG ML</t>
+          <t>Under 46.5</t>
         </is>
       </c>
       <c r="E128" s="12" t="n">
-        <v>-166</v>
+        <v>-110</v>
       </c>
       <c r="F128" s="13" t="n">
-        <v>0.6108</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="G128" s="13" t="n">
-        <v>0.6241</v>
+        <v>0.5238</v>
       </c>
       <c r="H128" s="13" t="n">
-        <v>0.01799261307474052</v>
+        <v>0.01482449180814355</v>
       </c>
       <c r="I128" s="13" t="n">
-        <v>-0.02106545831325304</v>
+        <v>-0.03094545454545439</v>
       </c>
       <c r="J128" s="15" t="n">
         <v>0.75</v>
@@ -10146,7 +10150,7 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>SEA @ WSH</t>
+          <t>NE @ JAX</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -10156,7 +10160,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Under 46.5</t>
+          <t>Under 45.5</t>
         </is>
       </c>
       <c r="E129" s="7" t="n">
@@ -10269,33 +10273,33 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>PIT @ NE</t>
+          <t>CAR @ CLE</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>CLE ML</t>
         </is>
       </c>
       <c r="E132" s="12" t="n">
-        <v>-105</v>
+        <v>105</v>
       </c>
       <c r="F132" s="13" t="n">
-        <v>0.4962</v>
+        <v>0.4724</v>
       </c>
       <c r="G132" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.4878</v>
       </c>
       <c r="H132" s="13" t="n">
-        <v>0.01399474306733005</v>
+        <v>0.01035621882133641</v>
       </c>
       <c r="I132" s="13" t="n">
-        <v>-0.03122857142857149</v>
+        <v>-0.03129578000000016</v>
       </c>
       <c r="J132" s="15" t="n">
         <v>0.75</v>
@@ -10310,33 +10314,33 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>CAR @ CLE</t>
+          <t>LV @ LAC</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>CLE ML</t>
+          <t>Over 43.5</t>
         </is>
       </c>
       <c r="E133" s="7" t="n">
-        <v>105</v>
+        <v>-110</v>
       </c>
       <c r="F133" s="8" t="n">
-        <v>0.4724</v>
+        <v>0.5051</v>
       </c>
       <c r="G133" s="8" t="n">
-        <v>0.4878</v>
+        <v>0.5238</v>
       </c>
       <c r="H133" s="8" t="n">
-        <v>0.01035621882133641</v>
+        <v>0.01008464914257048</v>
       </c>
       <c r="I133" s="8" t="n">
-        <v>-0.03129578000000016</v>
+        <v>-0.03571818181818176</v>
       </c>
       <c r="J133" s="10" t="n">
         <v>0.75</v>
@@ -10351,7 +10355,7 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>LV @ LAC</t>
+          <t>IND @ KC</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
@@ -10361,7 +10365,7 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>Over 43.5</t>
+          <t>Under 47.5</t>
         </is>
       </c>
       <c r="E134" s="12" t="n">
@@ -10884,33 +10888,33 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>GB @ NYJ</t>
+          <t>JAX @ CIN</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Over 44.5</t>
+          <t>CIN ML</t>
         </is>
       </c>
       <c r="E147" s="7" t="n">
-        <v>-112</v>
+        <v>-135</v>
       </c>
       <c r="F147" s="8" t="n">
-        <v>0.5066000000000001</v>
+        <v>0.5535</v>
       </c>
       <c r="G147" s="8" t="n">
-        <v>0.5283</v>
+        <v>0.5745</v>
       </c>
       <c r="H147" s="8" t="n">
-        <v>0.004550352289739427</v>
+        <v>0.003802412031205433</v>
       </c>
       <c r="I147" s="8" t="n">
-        <v>-0.04107857142857141</v>
+        <v>-0.03617515000000009</v>
       </c>
       <c r="J147" s="10" t="n">
         <v>0.75</v>
@@ -10930,28 +10934,28 @@
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>CIN ML</t>
+          <t>CIN -2.5</t>
         </is>
       </c>
       <c r="E148" s="12" t="n">
-        <v>-135</v>
+        <v>-110</v>
       </c>
       <c r="F148" s="13" t="n">
-        <v>0.5535</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="G148" s="13" t="n">
-        <v>0.5745</v>
+        <v>0.5238</v>
       </c>
       <c r="H148" s="13" t="n">
-        <v>0.003802412031205433</v>
+        <v>0.002997028329871269</v>
       </c>
       <c r="I148" s="13" t="n">
-        <v>-0.03617515000000009</v>
+        <v>-0.04259090909090912</v>
       </c>
       <c r="J148" s="15" t="n">
         <v>0.75</v>
@@ -10966,7 +10970,7 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>JAX @ CIN</t>
+          <t>MIN @ TB</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
@@ -10976,23 +10980,23 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>CIN -2.5</t>
+          <t>TB -1.5</t>
         </is>
       </c>
       <c r="E149" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F149" s="8" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.5002</v>
       </c>
       <c r="G149" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H149" s="8" t="n">
-        <v>0.002997028329871269</v>
+        <v>0.0003999929478075615</v>
       </c>
       <c r="I149" s="8" t="n">
-        <v>-0.04259090909090912</v>
+        <v>-0.04507272727272726</v>
       </c>
       <c r="J149" s="10" t="n">
         <v>0.75</v>
@@ -11007,33 +11011,33 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>MIN @ TB</t>
+          <t>ATL @ GB</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>TB -1.5</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="E150" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F150" s="13" t="n">
-        <v>0.5002</v>
+        <v>0.5</v>
       </c>
       <c r="G150" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H150" s="13" t="n">
-        <v>0.0003999929478075615</v>
+        <v>0</v>
       </c>
       <c r="I150" s="13" t="n">
-        <v>-0.04507272727272726</v>
+        <v>-0.04545454545454541</v>
       </c>
       <c r="J150" s="15" t="n">
         <v>0.75</v>
@@ -11048,33 +11052,33 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>MIN @ TB</t>
+          <t>ATL @ GB</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>MIN +1.5</t>
+          <t>Under 46.5</t>
         </is>
       </c>
       <c r="E151" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F151" s="8" t="n">
-        <v>0.4998</v>
+        <v>0.5</v>
       </c>
       <c r="G151" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H151" s="8" t="n">
-        <v>-0.0003999929478075615</v>
+        <v>0</v>
       </c>
       <c r="I151" s="8" t="n">
-        <v>-0.04583636363636356</v>
+        <v>-0.04545454545454541</v>
       </c>
       <c r="J151" s="10" t="n">
         <v>0.75</v>
@@ -11089,7 +11093,7 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>JAX @ CIN</t>
+          <t>MIN @ TB</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
@@ -11099,23 +11103,23 @@
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>JAX +2.5</t>
+          <t>MIN +1.5</t>
         </is>
       </c>
       <c r="E152" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F152" s="13" t="n">
-        <v>0.4985</v>
+        <v>0.4998</v>
       </c>
       <c r="G152" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H152" s="13" t="n">
-        <v>-0.00299702832987138</v>
+        <v>-0.0003999929478075615</v>
       </c>
       <c r="I152" s="13" t="n">
-        <v>-0.04831818181818182</v>
+        <v>-0.04583636363636356</v>
       </c>
       <c r="J152" s="15" t="n">
         <v>0.75</v>
@@ -11130,33 +11134,33 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>BAL @ DAL</t>
+          <t>JAX @ CIN</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>BAL ML</t>
+          <t>JAX +2.5</t>
         </is>
       </c>
       <c r="E153" s="7" t="n">
-        <v>-135</v>
+        <v>-110</v>
       </c>
       <c r="F153" s="8" t="n">
-        <v>0.5492</v>
+        <v>0.4985</v>
       </c>
       <c r="G153" s="8" t="n">
-        <v>0.5745</v>
+        <v>0.5238</v>
       </c>
       <c r="H153" s="8" t="n">
-        <v>-0.003982859973893956</v>
+        <v>-0.00299702832987138</v>
       </c>
       <c r="I153" s="8" t="n">
-        <v>-0.04359371703703698</v>
+        <v>-0.04831818181818182</v>
       </c>
       <c r="J153" s="10" t="n">
         <v>0.75</v>
@@ -11171,33 +11175,33 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>GB @ NYJ</t>
+          <t>BAL @ DAL</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>Under 44.5</t>
+          <t>BAL ML</t>
         </is>
       </c>
       <c r="E154" s="12" t="n">
-        <v>-108</v>
+        <v>-135</v>
       </c>
       <c r="F154" s="13" t="n">
-        <v>0.4934</v>
+        <v>0.5492</v>
       </c>
       <c r="G154" s="13" t="n">
-        <v>0.5192</v>
+        <v>0.5745</v>
       </c>
       <c r="H154" s="13" t="n">
-        <v>-0.004628927129813734</v>
+        <v>-0.003982859973893956</v>
       </c>
       <c r="I154" s="13" t="n">
-        <v>-0.0497481481481481</v>
+        <v>-0.04359371703703698</v>
       </c>
       <c r="J154" s="15" t="n">
         <v>0.75</v>
@@ -11622,7 +11626,7 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>LAR @ DEN</t>
+          <t>IND @ KC</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
@@ -11632,7 +11636,7 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>Under 45.5</t>
+          <t>Over 47.5</t>
         </is>
       </c>
       <c r="E165" s="7" t="n">
@@ -11663,33 +11667,33 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>DAL @ HOU</t>
+          <t>LAR @ DEN</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>DAL ML</t>
+          <t>Under 45.5</t>
         </is>
       </c>
       <c r="E166" s="12" t="n">
-        <v>114</v>
+        <v>-110</v>
       </c>
       <c r="F166" s="13" t="n">
-        <v>0.4439</v>
+        <v>0.4949</v>
       </c>
       <c r="G166" s="13" t="n">
-        <v>0.4673</v>
+        <v>0.5238</v>
       </c>
       <c r="H166" s="13" t="n">
-        <v>-0.01035212548018982</v>
+        <v>-0.01008464914257048</v>
       </c>
       <c r="I166" s="13" t="n">
-        <v>-0.04960851940000015</v>
+        <v>-0.05519090909090907</v>
       </c>
       <c r="J166" s="15" t="n">
         <v>0.75</v>
@@ -11704,7 +11708,7 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>ATL @ NO</t>
+          <t>DAL @ HOU</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
@@ -11714,23 +11718,23 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>ATL ML</t>
+          <t>DAL ML</t>
         </is>
       </c>
       <c r="E167" s="7" t="n">
         <v>114</v>
       </c>
       <c r="F167" s="8" t="n">
-        <v>0.4437</v>
+        <v>0.4439</v>
       </c>
       <c r="G167" s="8" t="n">
         <v>0.4673</v>
       </c>
       <c r="H167" s="8" t="n">
-        <v>-0.01078149800309135</v>
+        <v>-0.01035212548018982</v>
       </c>
       <c r="I167" s="8" t="n">
-        <v>-0.05003271020000014</v>
+        <v>-0.04960851940000015</v>
       </c>
       <c r="J167" s="10" t="n">
         <v>0.75</v>
@@ -11745,7 +11749,7 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>LAC @ SEA</t>
+          <t>ATL @ NO</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
@@ -11755,23 +11759,23 @@
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>LAC ML</t>
+          <t>ATL ML</t>
         </is>
       </c>
       <c r="E168" s="12" t="n">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="F168" s="13" t="n">
-        <v>0.3862</v>
+        <v>0.4437</v>
       </c>
       <c r="G168" s="13" t="n">
-        <v>0.4082</v>
+        <v>0.4673</v>
       </c>
       <c r="H168" s="13" t="n">
-        <v>-0.0115942528723451</v>
+        <v>-0.01078149800309135</v>
       </c>
       <c r="I168" s="13" t="n">
-        <v>-0.05334723399999991</v>
+        <v>-0.05003271020000014</v>
       </c>
       <c r="J168" s="15" t="n">
         <v>0.75</v>
@@ -11786,7 +11790,7 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>MIN @ TB</t>
+          <t>LAC @ SEA</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
@@ -11796,23 +11800,23 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>TB ML</t>
+          <t>LAC ML</t>
         </is>
       </c>
       <c r="E169" s="7" t="n">
-        <v>-130</v>
+        <v>145</v>
       </c>
       <c r="F169" s="8" t="n">
-        <v>0.5358000000000001</v>
+        <v>0.3862</v>
       </c>
       <c r="G169" s="8" t="n">
-        <v>0.5652</v>
+        <v>0.4082</v>
       </c>
       <c r="H169" s="8" t="n">
-        <v>-0.01249246977309075</v>
+        <v>-0.0115942528723451</v>
       </c>
       <c r="I169" s="8" t="n">
-        <v>-0.05157773846153836</v>
+        <v>-0.05334723399999991</v>
       </c>
       <c r="J169" s="10" t="n">
         <v>0.75</v>
@@ -11827,33 +11831,33 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>PIT @ NE</t>
+          <t>MIN @ TB</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>TB ML</t>
         </is>
       </c>
       <c r="E170" s="12" t="n">
-        <v>-115</v>
+        <v>-130</v>
       </c>
       <c r="F170" s="13" t="n">
-        <v>0.5038</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="G170" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.5652</v>
       </c>
       <c r="H170" s="13" t="n">
-        <v>-0.01342727100865891</v>
+        <v>-0.01249246977309075</v>
       </c>
       <c r="I170" s="13" t="n">
-        <v>-0.05811304347826085</v>
+        <v>-0.05157773846153836</v>
       </c>
       <c r="J170" s="15" t="n">
         <v>0.75</v>
@@ -11909,7 +11913,7 @@
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>TEN @ BAL</t>
+          <t>NE @ JAX</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
@@ -11919,7 +11923,7 @@
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
+          <t>Over 45.5</t>
         </is>
       </c>
       <c r="E172" s="12" t="n">
@@ -11950,7 +11954,7 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>ATL @ NO</t>
+          <t>TEN @ BAL</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
@@ -11960,23 +11964,23 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>Over 45.5</t>
+          <t>Over 47.5</t>
         </is>
       </c>
       <c r="E173" s="7" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="F173" s="8" t="n">
-        <v>0.5012</v>
+        <v>0.4924</v>
       </c>
       <c r="G173" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.5238</v>
       </c>
       <c r="H173" s="8" t="n">
-        <v>-0.01809517229067094</v>
+        <v>-0.01482449180814345</v>
       </c>
       <c r="I173" s="8" t="n">
-        <v>-0.06297391304347832</v>
+        <v>-0.05996363636363633</v>
       </c>
       <c r="J173" s="10" t="n">
         <v>0.75</v>
@@ -11991,33 +11995,33 @@
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>NE @ BUF</t>
+          <t>ATL @ NO</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>BUF -3</t>
+          <t>Over 45.5</t>
         </is>
       </c>
       <c r="E174" s="12" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F174" s="13" t="n">
-        <v>0.4905</v>
+        <v>0.5012</v>
       </c>
       <c r="G174" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5349</v>
       </c>
       <c r="H174" s="13" t="n">
-        <v>-0.01827860408321841</v>
+        <v>-0.01809517229067094</v>
       </c>
       <c r="I174" s="13" t="n">
-        <v>-0.05900600454545449</v>
+        <v>-0.06297391304347832</v>
       </c>
       <c r="J174" s="15" t="n">
         <v>0.75</v>
@@ -12037,28 +12041,28 @@
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>BUF ML</t>
+          <t>BUF -3</t>
         </is>
       </c>
       <c r="E175" s="7" t="n">
-        <v>-162</v>
+        <v>-110</v>
       </c>
       <c r="F175" s="8" t="n">
-        <v>0.5814</v>
+        <v>0.4905</v>
       </c>
       <c r="G175" s="8" t="n">
-        <v>0.6183</v>
+        <v>0.5238</v>
       </c>
       <c r="H175" s="8" t="n">
-        <v>-0.01935788332738309</v>
+        <v>-0.01827860408321841</v>
       </c>
       <c r="I175" s="8" t="n">
-        <v>-0.05918565333333327</v>
+        <v>-0.05900600454545449</v>
       </c>
       <c r="J175" s="10" t="n">
         <v>0.75</v>
@@ -12073,33 +12077,33 @@
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>GB @ TB</t>
+          <t>NE @ BUF</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
+          <t>BUF ML</t>
         </is>
       </c>
       <c r="E176" s="12" t="n">
-        <v>-110</v>
+        <v>-162</v>
       </c>
       <c r="F176" s="13" t="n">
-        <v>0.4898</v>
+        <v>0.5814</v>
       </c>
       <c r="G176" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.6183</v>
       </c>
       <c r="H176" s="13" t="n">
-        <v>-0.01951326459787421</v>
+        <v>-0.01935788332738309</v>
       </c>
       <c r="I176" s="13" t="n">
-        <v>-0.06492727272727261</v>
+        <v>-0.05918565333333327</v>
       </c>
       <c r="J176" s="15" t="n">
         <v>0.75</v>
@@ -12114,7 +12118,7 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>NO @ BAL</t>
+          <t>GB @ TB</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
@@ -12124,23 +12128,23 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>Under 46.5</t>
+          <t>Under 47.5</t>
         </is>
       </c>
       <c r="E177" s="7" t="n">
-        <v>-102</v>
+        <v>-110</v>
       </c>
       <c r="F177" s="8" t="n">
-        <v>0.4711</v>
+        <v>0.4898</v>
       </c>
       <c r="G177" s="8" t="n">
-        <v>0.505</v>
+        <v>0.5238</v>
       </c>
       <c r="H177" s="8" t="n">
-        <v>-0.02244228249560908</v>
+        <v>-0.01951326459787421</v>
       </c>
       <c r="I177" s="8" t="n">
-        <v>-0.06703725490196066</v>
+        <v>-0.06492727272727261</v>
       </c>
       <c r="J177" s="10" t="n">
         <v>0.75</v>
@@ -12155,33 +12159,33 @@
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>JAX @ DEN</t>
+          <t>NO @ BAL</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>DEN ML</t>
+          <t>Under 46.5</t>
         </is>
       </c>
       <c r="E178" s="12" t="n">
-        <v>-135</v>
+        <v>-102</v>
       </c>
       <c r="F178" s="13" t="n">
-        <v>0.5377</v>
+        <v>0.4711</v>
       </c>
       <c r="G178" s="13" t="n">
-        <v>0.5745</v>
+        <v>0.505</v>
       </c>
       <c r="H178" s="13" t="n">
-        <v>-0.02328317362397257</v>
+        <v>-0.02244228249560908</v>
       </c>
       <c r="I178" s="13" t="n">
-        <v>-0.06342767037037045</v>
+        <v>-0.06703725490196066</v>
       </c>
       <c r="J178" s="15" t="n">
         <v>0.75</v>
@@ -12196,7 +12200,7 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>CIN @ HOU</t>
+          <t>JAX @ DEN</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
@@ -12206,23 +12210,23 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>HOU ML</t>
+          <t>DEN ML</t>
         </is>
       </c>
       <c r="E179" s="7" t="n">
-        <v>-148</v>
+        <v>-135</v>
       </c>
       <c r="F179" s="8" t="n">
-        <v>0.5577</v>
+        <v>0.5377</v>
       </c>
       <c r="G179" s="8" t="n">
-        <v>0.5968</v>
+        <v>0.5745</v>
       </c>
       <c r="H179" s="8" t="n">
-        <v>-0.02354891730804846</v>
+        <v>-0.02328317362397257</v>
       </c>
       <c r="I179" s="8" t="n">
-        <v>-0.06489294216216218</v>
+        <v>-0.06342767037037045</v>
       </c>
       <c r="J179" s="10" t="n">
         <v>0.75</v>
@@ -12237,33 +12241,33 @@
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>MIA @ SF</t>
+          <t>CIN @ HOU</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>Under 45.5</t>
+          <t>HOU ML</t>
         </is>
       </c>
       <c r="E180" s="12" t="n">
-        <v>-112</v>
+        <v>-148</v>
       </c>
       <c r="F180" s="13" t="n">
-        <v>0.4913</v>
+        <v>0.5577</v>
       </c>
       <c r="G180" s="13" t="n">
-        <v>0.5283</v>
+        <v>0.5968</v>
       </c>
       <c r="H180" s="13" t="n">
-        <v>-0.02404300228152523</v>
+        <v>-0.02354891730804846</v>
       </c>
       <c r="I180" s="13" t="n">
-        <v>-0.07003928571428575</v>
+        <v>-0.06489294216216218</v>
       </c>
       <c r="J180" s="15" t="n">
         <v>0.75</v>
@@ -12278,33 +12282,33 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>LAC @ SEA</t>
+          <t>MIA @ SF</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>LAC +3</t>
+          <t>Under 45.5</t>
         </is>
       </c>
       <c r="E181" s="7" t="n">
-        <v>-105</v>
+        <v>-112</v>
       </c>
       <c r="F181" s="8" t="n">
-        <v>0.4765</v>
+        <v>0.4913</v>
       </c>
       <c r="G181" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.5283</v>
       </c>
       <c r="H181" s="8" t="n">
-        <v>-0.02419036905564134</v>
+        <v>-0.02404300228152523</v>
       </c>
       <c r="I181" s="8" t="n">
-        <v>-0.06466579285714295</v>
+        <v>-0.07003928571428575</v>
       </c>
       <c r="J181" s="10" t="n">
         <v>0.75</v>
@@ -12319,7 +12323,7 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>TEN @ NYG</t>
+          <t>LAC @ SEA</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
@@ -12329,23 +12333,23 @@
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>TEN +3</t>
+          <t>LAC +3</t>
         </is>
       </c>
       <c r="E182" s="12" t="n">
         <v>-105</v>
       </c>
       <c r="F182" s="13" t="n">
-        <v>0.4761</v>
+        <v>0.4765</v>
       </c>
       <c r="G182" s="13" t="n">
         <v>0.5122</v>
       </c>
       <c r="H182" s="13" t="n">
-        <v>-0.02484552512496846</v>
+        <v>-0.02419036905564134</v>
       </c>
       <c r="I182" s="13" t="n">
-        <v>-0.06539043857142852</v>
+        <v>-0.06466579285714295</v>
       </c>
       <c r="J182" s="15" t="n">
         <v>0.75</v>
@@ -12360,33 +12364,33 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>MIN @ CHI</t>
+          <t>TEN @ NYG</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>Under 49.5</t>
+          <t>TEN +3</t>
         </is>
       </c>
       <c r="E183" s="7" t="n">
-        <v>-118</v>
+        <v>-105</v>
       </c>
       <c r="F183" s="8" t="n">
-        <v>0.5034999999999999</v>
+        <v>0.4761</v>
       </c>
       <c r="G183" s="8" t="n">
-        <v>0.5413</v>
+        <v>0.5122</v>
       </c>
       <c r="H183" s="8" t="n">
-        <v>-0.02491446829994306</v>
+        <v>-0.02484552512496846</v>
       </c>
       <c r="I183" s="8" t="n">
-        <v>-0.06980508474576286</v>
+        <v>-0.06539043857142852</v>
       </c>
       <c r="J183" s="10" t="n">
         <v>0.75</v>
@@ -12401,33 +12405,33 @@
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>TEN @ NYG</t>
+          <t>MIN @ CHI</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>TEN ML</t>
+          <t>Under 49.5</t>
         </is>
       </c>
       <c r="E184" s="12" t="n">
-        <v>140</v>
+        <v>-118</v>
       </c>
       <c r="F184" s="13" t="n">
-        <v>0.3892</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="G184" s="13" t="n">
-        <v>0.4167</v>
+        <v>0.5413</v>
       </c>
       <c r="H184" s="13" t="n">
-        <v>-0.02578619345701206</v>
+        <v>-0.02491446829994306</v>
       </c>
       <c r="I184" s="13" t="n">
-        <v>-0.06535308800000009</v>
+        <v>-0.06980508474576286</v>
       </c>
       <c r="J184" s="15" t="n">
         <v>0.75</v>
@@ -12442,33 +12446,33 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>JAX @ DEN</t>
+          <t>TEN @ NYG</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>DEN -2.5</t>
+          <t>TEN ML</t>
         </is>
       </c>
       <c r="E185" s="7" t="n">
-        <v>-110</v>
+        <v>140</v>
       </c>
       <c r="F185" s="8" t="n">
-        <v>0.4858</v>
+        <v>0.3892</v>
       </c>
       <c r="G185" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.4167</v>
       </c>
       <c r="H185" s="8" t="n">
-        <v>-0.02611887220744774</v>
+        <v>-0.02578619345701206</v>
       </c>
       <c r="I185" s="8" t="n">
-        <v>-0.07256363636363627</v>
+        <v>-0.06535308800000009</v>
       </c>
       <c r="J185" s="10" t="n">
         <v>0.75</v>
@@ -12483,33 +12487,33 @@
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>IND @ KC</t>
+          <t>JAX @ DEN</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
+          <t>DEN -2.5</t>
         </is>
       </c>
       <c r="E186" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F186" s="13" t="n">
-        <v>0.4847</v>
+        <v>0.4858</v>
       </c>
       <c r="G186" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H186" s="13" t="n">
-        <v>-0.02779009306515143</v>
+        <v>-0.02611887220744774</v>
       </c>
       <c r="I186" s="13" t="n">
-        <v>-0.07466363636363627</v>
+        <v>-0.07256363636363627</v>
       </c>
       <c r="J186" s="15" t="n">
         <v>0.75</v>
@@ -13098,7 +13102,7 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>NE @ JAX</t>
+          <t>KC @ MIA</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
@@ -13108,7 +13112,7 @@
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>Over 45.5</t>
+          <t>Under 44.5</t>
         </is>
       </c>
       <c r="E201" s="7" t="n">
@@ -13836,7 +13840,7 @@
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>ATL @ GB</t>
+          <t>HOU @ IND</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
@@ -13846,7 +13850,7 @@
       </c>
       <c r="D219" s="4" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
+          <t>Under 45.5</t>
         </is>
       </c>
       <c r="E219" s="7" t="n">
@@ -13877,7 +13881,7 @@
       </c>
       <c r="B220" s="5" t="inlineStr">
         <is>
-          <t>HOU @ IND</t>
+          <t>JAX @ DEN</t>
         </is>
       </c>
       <c r="C220" s="5" t="inlineStr">
@@ -13887,23 +13891,23 @@
       </c>
       <c r="D220" s="5" t="inlineStr">
         <is>
-          <t>Under 45.5</t>
+          <t>Under 44.5</t>
         </is>
       </c>
       <c r="E220" s="12" t="n">
-        <v>-110</v>
+        <v>-118</v>
       </c>
       <c r="F220" s="13" t="n">
-        <v>0.4721</v>
+        <v>0.4883</v>
       </c>
       <c r="G220" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5413</v>
       </c>
       <c r="H220" s="13" t="n">
-        <v>-0.04221995376217116</v>
+        <v>-0.04240068716248256</v>
       </c>
       <c r="I220" s="13" t="n">
-        <v>-0.09871818181818171</v>
+        <v>-0.09788644067796615</v>
       </c>
       <c r="J220" s="15" t="n">
         <v>0.75</v>
@@ -13918,33 +13922,33 @@
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>JAX @ DEN</t>
+          <t>LAR @ PHI</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D221" s="4" t="inlineStr">
         <is>
-          <t>Under 44.5</t>
+          <t>LAR ML</t>
         </is>
       </c>
       <c r="E221" s="7" t="n">
-        <v>-118</v>
+        <v>-122</v>
       </c>
       <c r="F221" s="8" t="n">
-        <v>0.4883</v>
+        <v>0.4962</v>
       </c>
       <c r="G221" s="8" t="n">
-        <v>0.5413</v>
+        <v>0.5495</v>
       </c>
       <c r="H221" s="8" t="n">
-        <v>-0.04240068716248256</v>
+        <v>-0.04263828533225695</v>
       </c>
       <c r="I221" s="8" t="n">
-        <v>-0.09788644067796615</v>
+        <v>-0.09620498032786892</v>
       </c>
       <c r="J221" s="10" t="n">
         <v>0.75</v>
@@ -13959,7 +13963,7 @@
       </c>
       <c r="B222" s="5" t="inlineStr">
         <is>
-          <t>LAR @ PHI</t>
+          <t>PHI @ CHI</t>
         </is>
       </c>
       <c r="C222" s="5" t="inlineStr">
@@ -13969,23 +13973,23 @@
       </c>
       <c r="D222" s="5" t="inlineStr">
         <is>
-          <t>LAR ML</t>
+          <t>PHI ML</t>
         </is>
       </c>
       <c r="E222" s="12" t="n">
-        <v>-122</v>
+        <v>-102</v>
       </c>
       <c r="F222" s="13" t="n">
-        <v>0.4962</v>
+        <v>0.4549</v>
       </c>
       <c r="G222" s="13" t="n">
-        <v>0.5495</v>
+        <v>0.505</v>
       </c>
       <c r="H222" s="13" t="n">
-        <v>-0.04263828533225695</v>
+        <v>-0.04286158962858524</v>
       </c>
       <c r="I222" s="13" t="n">
-        <v>-0.09620498032786892</v>
+        <v>-0.0982374433333333</v>
       </c>
       <c r="J222" s="15" t="n">
         <v>0.75</v>
@@ -14000,33 +14004,33 @@
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>PHI @ CHI</t>
+          <t>NE @ JAX</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr">
         <is>
-          <t>PHI ML</t>
+          <t>NE +1.5</t>
         </is>
       </c>
       <c r="E223" s="7" t="n">
-        <v>-102</v>
+        <v>-115</v>
       </c>
       <c r="F223" s="8" t="n">
-        <v>0.4549</v>
+        <v>0.4805</v>
       </c>
       <c r="G223" s="8" t="n">
-        <v>0.505</v>
+        <v>0.5349</v>
       </c>
       <c r="H223" s="8" t="n">
-        <v>-0.04286158962858524</v>
+        <v>-0.04359577192025565</v>
       </c>
       <c r="I223" s="8" t="n">
-        <v>-0.0982374433333333</v>
+        <v>-0.1016739130434784</v>
       </c>
       <c r="J223" s="10" t="n">
         <v>0.75</v>
@@ -14041,33 +14045,33 @@
       </c>
       <c r="B224" s="5" t="inlineStr">
         <is>
-          <t>NE @ JAX</t>
+          <t>CIN @ HOU</t>
         </is>
       </c>
       <c r="C224" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D224" s="5" t="inlineStr">
         <is>
-          <t>NE +1.5</t>
+          <t>Under 46.5</t>
         </is>
       </c>
       <c r="E224" s="12" t="n">
-        <v>-115</v>
+        <v>-112</v>
       </c>
       <c r="F224" s="13" t="n">
-        <v>0.4805</v>
+        <v>0.4736</v>
       </c>
       <c r="G224" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.5283</v>
       </c>
       <c r="H224" s="13" t="n">
-        <v>-0.04359577192025565</v>
+        <v>-0.04416193300989845</v>
       </c>
       <c r="I224" s="13" t="n">
-        <v>-0.1016739130434784</v>
+        <v>-0.1035428571428572</v>
       </c>
       <c r="J224" s="15" t="n">
         <v>0.75</v>
@@ -14082,7 +14086,7 @@
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>CIN @ HOU</t>
+          <t>GB @ NYJ</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
@@ -14092,23 +14096,23 @@
       </c>
       <c r="D225" s="4" t="inlineStr">
         <is>
-          <t>Under 46.5</t>
+          <t>Under 44.5</t>
         </is>
       </c>
       <c r="E225" s="7" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="F225" s="8" t="n">
-        <v>0.4736</v>
+        <v>0.4655</v>
       </c>
       <c r="G225" s="8" t="n">
-        <v>0.5283</v>
+        <v>0.5192</v>
       </c>
       <c r="H225" s="8" t="n">
-        <v>-0.04416193300989845</v>
+        <v>-0.04417879128772354</v>
       </c>
       <c r="I225" s="8" t="n">
-        <v>-0.1035428571428572</v>
+        <v>-0.1034814814814814</v>
       </c>
       <c r="J225" s="10" t="n">
         <v>0.75</v>
@@ -14123,33 +14127,33 @@
       </c>
       <c r="B226" s="5" t="inlineStr">
         <is>
-          <t>KC @ MIA</t>
+          <t>TB @ DAL</t>
         </is>
       </c>
       <c r="C226" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D226" s="5" t="inlineStr">
         <is>
-          <t>Under 44.5</t>
+          <t>DAL ML</t>
         </is>
       </c>
       <c r="E226" s="12" t="n">
-        <v>-110</v>
+        <v>-205</v>
       </c>
       <c r="F226" s="13" t="n">
-        <v>0.4695</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="G226" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.6721</v>
       </c>
       <c r="H226" s="13" t="n">
-        <v>-0.04420574441993441</v>
+        <v>-0.0442459261696939</v>
       </c>
       <c r="I226" s="13" t="n">
-        <v>-0.1036818181818182</v>
+        <v>-0.09855670829268305</v>
       </c>
       <c r="J226" s="15" t="n">
         <v>0.75</v>
@@ -14164,7 +14168,7 @@
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>TB @ DAL</t>
+          <t>ARI @ NYG</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
@@ -14174,23 +14178,23 @@
       </c>
       <c r="D227" s="4" t="inlineStr">
         <is>
-          <t>DAL ML</t>
+          <t>NYG ML</t>
         </is>
       </c>
       <c r="E227" s="7" t="n">
-        <v>-205</v>
+        <v>-325</v>
       </c>
       <c r="F227" s="8" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.6883</v>
       </c>
       <c r="G227" s="8" t="n">
-        <v>0.6721</v>
+        <v>0.7647</v>
       </c>
       <c r="H227" s="8" t="n">
-        <v>-0.0442459261696939</v>
+        <v>-0.04442406488990254</v>
       </c>
       <c r="I227" s="8" t="n">
-        <v>-0.09855670829268305</v>
+        <v>-0.09909607846153848</v>
       </c>
       <c r="J227" s="10" t="n">
         <v>0.75</v>
@@ -14205,33 +14209,33 @@
       </c>
       <c r="B228" s="5" t="inlineStr">
         <is>
-          <t>ARI @ NYG</t>
+          <t>DET @ BUF</t>
         </is>
       </c>
       <c r="C228" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D228" s="5" t="inlineStr">
         <is>
-          <t>NYG ML</t>
+          <t>BUF -4.5</t>
         </is>
       </c>
       <c r="E228" s="12" t="n">
-        <v>-325</v>
+        <v>-108</v>
       </c>
       <c r="F228" s="13" t="n">
-        <v>0.6883</v>
+        <v>0.4647</v>
       </c>
       <c r="G228" s="13" t="n">
-        <v>0.7647</v>
+        <v>0.5192</v>
       </c>
       <c r="H228" s="13" t="n">
-        <v>-0.04442406488990254</v>
+        <v>-0.04473803482567871</v>
       </c>
       <c r="I228" s="13" t="n">
-        <v>-0.09909607846153848</v>
+        <v>-0.1050222222222221</v>
       </c>
       <c r="J228" s="15" t="n">
         <v>0.75</v>
@@ -14246,33 +14250,33 @@
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>DET @ BUF</t>
+          <t>MIN @ CHI</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D229" s="4" t="inlineStr">
         <is>
-          <t>BUF -4.5</t>
+          <t>CHI ML</t>
         </is>
       </c>
       <c r="E229" s="7" t="n">
-        <v>-108</v>
+        <v>-238</v>
       </c>
       <c r="F229" s="8" t="n">
-        <v>0.4647</v>
+        <v>0.6326000000000001</v>
       </c>
       <c r="G229" s="8" t="n">
-        <v>0.5192</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="H229" s="8" t="n">
-        <v>-0.04473803482567871</v>
+        <v>-0.0448313710395704</v>
       </c>
       <c r="I229" s="8" t="n">
-        <v>-0.1050222222222221</v>
+        <v>-0.1007279062184873</v>
       </c>
       <c r="J229" s="10" t="n">
         <v>0.75</v>
@@ -14287,7 +14291,7 @@
       </c>
       <c r="B230" s="5" t="inlineStr">
         <is>
-          <t>MIN @ CHI</t>
+          <t>TEN @ BAL</t>
         </is>
       </c>
       <c r="C230" s="5" t="inlineStr">
@@ -14297,28 +14301,32 @@
       </c>
       <c r="D230" s="5" t="inlineStr">
         <is>
-          <t>CHI ML</t>
+          <t>BAL ML</t>
         </is>
       </c>
       <c r="E230" s="12" t="n">
-        <v>-238</v>
+        <v>-380</v>
       </c>
       <c r="F230" s="13" t="n">
-        <v>0.6326000000000001</v>
+        <v>0.7117</v>
       </c>
       <c r="G230" s="13" t="n">
-        <v>0.7040999999999999</v>
+        <v>0.7917</v>
       </c>
       <c r="H230" s="13" t="n">
-        <v>-0.0448313710395704</v>
+        <v>-0.04507627946268847</v>
       </c>
       <c r="I230" s="13" t="n">
-        <v>-0.1007279062184873</v>
+        <v>-0.1002024421052632</v>
       </c>
       <c r="J230" s="15" t="n">
         <v>0.75</v>
       </c>
-      <c r="K230" s="5" t="inlineStr"/>
+      <c r="K230" s="5" t="inlineStr">
+        <is>
+          <t>price -380 outside the allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
@@ -14328,42 +14336,38 @@
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>TEN @ BAL</t>
+          <t>TEN @ NYG</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D231" s="4" t="inlineStr">
         <is>
-          <t>BAL ML</t>
+          <t>Under 44.5</t>
         </is>
       </c>
       <c r="E231" s="7" t="n">
-        <v>-380</v>
+        <v>-110</v>
       </c>
       <c r="F231" s="8" t="n">
-        <v>0.7117</v>
+        <v>0.467</v>
       </c>
       <c r="G231" s="8" t="n">
-        <v>0.7917</v>
+        <v>0.5238</v>
       </c>
       <c r="H231" s="8" t="n">
-        <v>-0.04507627946268847</v>
+        <v>-0.04585100338566853</v>
       </c>
       <c r="I231" s="8" t="n">
-        <v>-0.1002024421052632</v>
+        <v>-0.1084545454545454</v>
       </c>
       <c r="J231" s="10" t="n">
         <v>0.75</v>
       </c>
-      <c r="K231" s="4" t="inlineStr">
-        <is>
-          <t>price -380 outside the allowed range</t>
-        </is>
-      </c>
+      <c r="K231" s="4" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="5" t="inlineStr">
@@ -14373,33 +14377,33 @@
       </c>
       <c r="B232" s="5" t="inlineStr">
         <is>
-          <t>TEN @ NYG</t>
+          <t>LAR @ PHI</t>
         </is>
       </c>
       <c r="C232" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D232" s="5" t="inlineStr">
         <is>
-          <t>Under 44.5</t>
+          <t>LAR -1.5</t>
         </is>
       </c>
       <c r="E232" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F232" s="13" t="n">
-        <v>0.467</v>
+        <v>0.4668</v>
       </c>
       <c r="G232" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H232" s="13" t="n">
-        <v>-0.04585100338566853</v>
+        <v>-0.045972273989346</v>
       </c>
       <c r="I232" s="13" t="n">
-        <v>-0.1084545454545454</v>
+        <v>-0.1088363636363636</v>
       </c>
       <c r="J232" s="15" t="n">
         <v>0.75</v>
@@ -14414,33 +14418,33 @@
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>LAR @ PHI</t>
+          <t>NE @ JAX</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D233" s="4" t="inlineStr">
         <is>
-          <t>LAR -1.5</t>
+          <t>NE ML</t>
         </is>
       </c>
       <c r="E233" s="7" t="n">
-        <v>-110</v>
+        <v>-102</v>
       </c>
       <c r="F233" s="8" t="n">
-        <v>0.4668</v>
+        <v>0.4499</v>
       </c>
       <c r="G233" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.505</v>
       </c>
       <c r="H233" s="8" t="n">
-        <v>-0.045972273989346</v>
+        <v>-0.04637313114533466</v>
       </c>
       <c r="I233" s="8" t="n">
-        <v>-0.1088363636363636</v>
+        <v>-0.1080512766666666</v>
       </c>
       <c r="J233" s="10" t="n">
         <v>0.75</v>
@@ -14455,7 +14459,7 @@
       </c>
       <c r="B234" s="5" t="inlineStr">
         <is>
-          <t>NE @ JAX</t>
+          <t>MIA @ SF</t>
         </is>
       </c>
       <c r="C234" s="5" t="inlineStr">
@@ -14465,28 +14469,32 @@
       </c>
       <c r="D234" s="5" t="inlineStr">
         <is>
-          <t>NE ML</t>
+          <t>SF ML</t>
         </is>
       </c>
       <c r="E234" s="12" t="n">
-        <v>-102</v>
+        <v>-950</v>
       </c>
       <c r="F234" s="13" t="n">
-        <v>0.4499</v>
+        <v>0.8087</v>
       </c>
       <c r="G234" s="13" t="n">
-        <v>0.505</v>
+        <v>0.9048</v>
       </c>
       <c r="H234" s="13" t="n">
-        <v>-0.04637313114533466</v>
+        <v>-0.04644165048849232</v>
       </c>
       <c r="I234" s="13" t="n">
-        <v>-0.1080512766666666</v>
+        <v>-0.1054623205263159</v>
       </c>
       <c r="J234" s="15" t="n">
         <v>0.75</v>
       </c>
-      <c r="K234" s="5" t="inlineStr"/>
+      <c r="K234" s="5" t="inlineStr">
+        <is>
+          <t>price -950 outside the allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="4" t="inlineStr">
@@ -14496,7 +14504,7 @@
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>MIA @ SF</t>
+          <t>DEN @ SF</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
@@ -14506,32 +14514,28 @@
       </c>
       <c r="D235" s="4" t="inlineStr">
         <is>
-          <t>SF ML</t>
+          <t>DEN ML</t>
         </is>
       </c>
       <c r="E235" s="7" t="n">
-        <v>-950</v>
+        <v>120</v>
       </c>
       <c r="F235" s="8" t="n">
-        <v>0.8087</v>
+        <v>0.4068</v>
       </c>
       <c r="G235" s="8" t="n">
-        <v>0.9048</v>
+        <v>0.4545</v>
       </c>
       <c r="H235" s="8" t="n">
-        <v>-0.04644165048849232</v>
+        <v>-0.04645466717275511</v>
       </c>
       <c r="I235" s="8" t="n">
-        <v>-0.1054623205263159</v>
+        <v>-0.1041366559999999</v>
       </c>
       <c r="J235" s="10" t="n">
         <v>0.75</v>
       </c>
-      <c r="K235" s="4" t="inlineStr">
-        <is>
-          <t>price -950 outside the allowed range</t>
-        </is>
-      </c>
+      <c r="K235" s="4" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="5" t="inlineStr">
@@ -14541,33 +14545,33 @@
       </c>
       <c r="B236" s="5" t="inlineStr">
         <is>
-          <t>DEN @ SF</t>
+          <t>PIT @ NE</t>
         </is>
       </c>
       <c r="C236" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D236" s="5" t="inlineStr">
         <is>
-          <t>DEN ML</t>
+          <t>Under 42.5</t>
         </is>
       </c>
       <c r="E236" s="12" t="n">
-        <v>120</v>
+        <v>-115</v>
       </c>
       <c r="F236" s="13" t="n">
-        <v>0.4068</v>
+        <v>0.4759</v>
       </c>
       <c r="G236" s="13" t="n">
-        <v>0.4545</v>
+        <v>0.5349</v>
       </c>
       <c r="H236" s="13" t="n">
-        <v>-0.04645466717275511</v>
+        <v>-0.04653541188972719</v>
       </c>
       <c r="I236" s="13" t="n">
-        <v>-0.1041366559999999</v>
+        <v>-0.1102739130434783</v>
       </c>
       <c r="J236" s="15" t="n">
         <v>0.75</v>
@@ -14623,38 +14627,42 @@
       </c>
       <c r="B238" s="5" t="inlineStr">
         <is>
-          <t>MIN @ TB</t>
+          <t>NYJ @ DET</t>
         </is>
       </c>
       <c r="C238" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D238" s="5" t="inlineStr">
         <is>
-          <t>Under 44.5</t>
+          <t>DET ML</t>
         </is>
       </c>
       <c r="E238" s="12" t="n">
-        <v>-110</v>
+        <v>-410</v>
       </c>
       <c r="F238" s="13" t="n">
-        <v>0.4645</v>
+        <v>0.7168</v>
       </c>
       <c r="G238" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="H238" s="13" t="n">
-        <v>-0.04726504445816375</v>
+        <v>-0.04723907528816788</v>
       </c>
       <c r="I238" s="13" t="n">
-        <v>-0.1132272727272726</v>
+        <v>-0.1075037658536585</v>
       </c>
       <c r="J238" s="15" t="n">
         <v>0.75</v>
       </c>
-      <c r="K238" s="5" t="inlineStr"/>
+      <c r="K238" s="5" t="inlineStr">
+        <is>
+          <t>price -410 outside the allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="4" t="inlineStr">
@@ -14664,42 +14672,38 @@
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>NYJ @ DET</t>
+          <t>DEN @ SF</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D239" s="4" t="inlineStr">
         <is>
-          <t>DET ML</t>
+          <t>DEN +2.5</t>
         </is>
       </c>
       <c r="E239" s="7" t="n">
-        <v>-410</v>
+        <v>-110</v>
       </c>
       <c r="F239" s="8" t="n">
-        <v>0.7164</v>
+        <v>0.4629</v>
       </c>
       <c r="G239" s="8" t="n">
-        <v>0.8038999999999999</v>
+        <v>0.5238</v>
       </c>
       <c r="H239" s="8" t="n">
-        <v>-0.04737397597953431</v>
+        <v>-0.04806111990959907</v>
       </c>
       <c r="I239" s="8" t="n">
-        <v>-0.1079973463414633</v>
+        <v>-0.1162818181818182</v>
       </c>
       <c r="J239" s="10" t="n">
         <v>0.75</v>
       </c>
-      <c r="K239" s="4" t="inlineStr">
-        <is>
-          <t>price -410 outside the allowed range</t>
-        </is>
-      </c>
+      <c r="K239" s="4" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="5" t="inlineStr">
@@ -14709,38 +14713,42 @@
       </c>
       <c r="B240" s="5" t="inlineStr">
         <is>
-          <t>DEN @ SF</t>
+          <t>ARI @ SF</t>
         </is>
       </c>
       <c r="C240" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D240" s="5" t="inlineStr">
         <is>
-          <t>DEN +2.5</t>
+          <t>SF ML</t>
         </is>
       </c>
       <c r="E240" s="12" t="n">
-        <v>-110</v>
+        <v>-650</v>
       </c>
       <c r="F240" s="13" t="n">
-        <v>0.4629</v>
+        <v>0.7696</v>
       </c>
       <c r="G240" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.8667</v>
       </c>
       <c r="H240" s="13" t="n">
-        <v>-0.04806111990959907</v>
+        <v>-0.0481445896883447</v>
       </c>
       <c r="I240" s="13" t="n">
-        <v>-0.1162818181818182</v>
+        <v>-0.1111712000000001</v>
       </c>
       <c r="J240" s="15" t="n">
         <v>0.75</v>
       </c>
-      <c r="K240" s="5" t="inlineStr"/>
+      <c r="K240" s="5" t="inlineStr">
+        <is>
+          <t>price -650 outside the allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="4" t="inlineStr">
@@ -14750,7 +14758,7 @@
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>ARI @ SF</t>
+          <t>DET @ CAR</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
@@ -14760,32 +14768,28 @@
       </c>
       <c r="D241" s="4" t="inlineStr">
         <is>
-          <t>SF ML</t>
+          <t>DET ML</t>
         </is>
       </c>
       <c r="E241" s="7" t="n">
-        <v>-650</v>
+        <v>-162</v>
       </c>
       <c r="F241" s="8" t="n">
-        <v>0.7696</v>
+        <v>0.5491</v>
       </c>
       <c r="G241" s="8" t="n">
-        <v>0.8667</v>
+        <v>0.6183</v>
       </c>
       <c r="H241" s="8" t="n">
-        <v>-0.0481445896883447</v>
+        <v>-0.0481678015336136</v>
       </c>
       <c r="I241" s="8" t="n">
-        <v>-0.1111712000000001</v>
+        <v>-0.1109418382716048</v>
       </c>
       <c r="J241" s="10" t="n">
         <v>0.75</v>
       </c>
-      <c r="K241" s="4" t="inlineStr">
-        <is>
-          <t>price -650 outside the allowed range</t>
-        </is>
-      </c>
+      <c r="K241" s="4" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="5" t="inlineStr">
@@ -14795,7 +14799,7 @@
       </c>
       <c r="B242" s="5" t="inlineStr">
         <is>
-          <t>DET @ CAR</t>
+          <t>KC @ LV</t>
         </is>
       </c>
       <c r="C242" s="5" t="inlineStr">
@@ -14805,23 +14809,23 @@
       </c>
       <c r="D242" s="5" t="inlineStr">
         <is>
-          <t>DET ML</t>
+          <t>KC ML</t>
         </is>
       </c>
       <c r="E242" s="12" t="n">
-        <v>-162</v>
+        <v>-230</v>
       </c>
       <c r="F242" s="13" t="n">
-        <v>0.5491</v>
+        <v>0.6186</v>
       </c>
       <c r="G242" s="13" t="n">
-        <v>0.6183</v>
+        <v>0.697</v>
       </c>
       <c r="H242" s="13" t="n">
-        <v>-0.0481678015336136</v>
+        <v>-0.04832495293575943</v>
       </c>
       <c r="I242" s="13" t="n">
-        <v>-0.1109418382716048</v>
+        <v>-0.11146522</v>
       </c>
       <c r="J242" s="15" t="n">
         <v>0.75</v>
@@ -14836,33 +14840,33 @@
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>KC @ LV</t>
+          <t>SEA @ ARI</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D243" s="4" t="inlineStr">
         <is>
-          <t>KC ML</t>
+          <t>Under 41.5</t>
         </is>
       </c>
       <c r="E243" s="7" t="n">
-        <v>-230</v>
+        <v>-110</v>
       </c>
       <c r="F243" s="8" t="n">
-        <v>0.6186</v>
+        <v>0.462</v>
       </c>
       <c r="G243" s="8" t="n">
-        <v>0.697</v>
+        <v>0.5238</v>
       </c>
       <c r="H243" s="8" t="n">
-        <v>-0.04832495293575943</v>
+        <v>-0.04847467639497064</v>
       </c>
       <c r="I243" s="8" t="n">
-        <v>-0.11146522</v>
+        <v>-0.1179999999999999</v>
       </c>
       <c r="J243" s="10" t="n">
         <v>0.75</v>
@@ -14877,38 +14881,42 @@
       </c>
       <c r="B244" s="5" t="inlineStr">
         <is>
-          <t>SEA @ ARI</t>
+          <t>NYJ @ CHI</t>
         </is>
       </c>
       <c r="C244" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D244" s="5" t="inlineStr">
         <is>
-          <t>Under 41.5</t>
+          <t>CHI ML</t>
         </is>
       </c>
       <c r="E244" s="12" t="n">
-        <v>-110</v>
+        <v>-410</v>
       </c>
       <c r="F244" s="13" t="n">
-        <v>0.462</v>
+        <v>0.7119</v>
       </c>
       <c r="G244" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="H244" s="13" t="n">
-        <v>-0.04847467639497064</v>
+        <v>-0.0487486134133566</v>
       </c>
       <c r="I244" s="13" t="n">
-        <v>-0.1179999999999999</v>
+        <v>-0.1135386802439024</v>
       </c>
       <c r="J244" s="15" t="n">
         <v>0.75</v>
       </c>
-      <c r="K244" s="5" t="inlineStr"/>
+      <c r="K244" s="5" t="inlineStr">
+        <is>
+          <t>price -410 outside the allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
@@ -15004,7 +15012,7 @@
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>NYJ @ CHI</t>
+          <t>CLE @ TB</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
@@ -15014,23 +15022,23 @@
       </c>
       <c r="D247" s="4" t="inlineStr">
         <is>
-          <t>CHI ML</t>
+          <t>TB ML</t>
         </is>
       </c>
       <c r="E247" s="7" t="n">
         <v>-410</v>
       </c>
       <c r="F247" s="8" t="n">
-        <v>0.7111</v>
+        <v>0.7099</v>
       </c>
       <c r="G247" s="8" t="n">
         <v>0.8038999999999999</v>
       </c>
       <c r="H247" s="8" t="n">
-        <v>-0.04896725833500191</v>
+        <v>-0.0492817571069234</v>
       </c>
       <c r="I247" s="8" t="n">
-        <v>-0.1145257417073172</v>
+        <v>-0.116006333902439</v>
       </c>
       <c r="J247" s="10" t="n">
         <v>0.75</v>
@@ -15049,42 +15057,38 @@
       </c>
       <c r="B248" s="5" t="inlineStr">
         <is>
-          <t>CLE @ TB</t>
+          <t>PIT @ NE</t>
         </is>
       </c>
       <c r="C248" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D248" s="5" t="inlineStr">
         <is>
-          <t>TB ML</t>
+          <t>NE -5.5</t>
         </is>
       </c>
       <c r="E248" s="12" t="n">
-        <v>-410</v>
+        <v>-110</v>
       </c>
       <c r="F248" s="13" t="n">
-        <v>0.7099</v>
+        <v>0.4593</v>
       </c>
       <c r="G248" s="13" t="n">
-        <v>0.8038999999999999</v>
+        <v>0.5238</v>
       </c>
       <c r="H248" s="13" t="n">
-        <v>-0.0492817571069234</v>
+        <v>-0.04958073933075707</v>
       </c>
       <c r="I248" s="13" t="n">
-        <v>-0.116006333902439</v>
+        <v>-0.1231545454545454</v>
       </c>
       <c r="J248" s="15" t="n">
         <v>0.75</v>
       </c>
-      <c r="K248" s="5" t="inlineStr">
-        <is>
-          <t>price -410 outside the allowed range</t>
-        </is>
-      </c>
+      <c r="K248" s="5" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
@@ -15094,33 +15098,33 @@
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>PIT @ NE</t>
+          <t>GB @ NYJ</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D249" s="4" t="inlineStr">
         <is>
-          <t>NE -5.5</t>
+          <t>GB ML</t>
         </is>
       </c>
       <c r="E249" s="7" t="n">
-        <v>-110</v>
+        <v>-205</v>
       </c>
       <c r="F249" s="8" t="n">
-        <v>0.4593</v>
+        <v>0.5898</v>
       </c>
       <c r="G249" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.6721</v>
       </c>
       <c r="H249" s="8" t="n">
-        <v>-0.04958073933075707</v>
+        <v>-0.050242649287872</v>
       </c>
       <c r="I249" s="8" t="n">
-        <v>-0.1231545454545454</v>
+        <v>-0.1214024980487805</v>
       </c>
       <c r="J249" s="10" t="n">
         <v>0.75</v>
@@ -15135,33 +15139,33 @@
       </c>
       <c r="B250" s="5" t="inlineStr">
         <is>
-          <t>GB @ NYJ</t>
+          <t>DET @ CAR</t>
         </is>
       </c>
       <c r="C250" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D250" s="5" t="inlineStr">
         <is>
-          <t>GB ML</t>
+          <t>DET -3</t>
         </is>
       </c>
       <c r="E250" s="12" t="n">
-        <v>-205</v>
+        <v>-110</v>
       </c>
       <c r="F250" s="13" t="n">
-        <v>0.5891</v>
+        <v>0.4564</v>
       </c>
       <c r="G250" s="13" t="n">
-        <v>0.6721</v>
+        <v>0.5238</v>
       </c>
       <c r="H250" s="13" t="n">
-        <v>-0.05041915319189092</v>
+        <v>-0.05056972123582924</v>
       </c>
       <c r="I250" s="13" t="n">
-        <v>-0.1224346924390245</v>
+        <v>-0.1195538545454545</v>
       </c>
       <c r="J250" s="15" t="n">
         <v>0.75</v>
@@ -15176,33 +15180,33 @@
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>DET @ CAR</t>
+          <t>SEA @ ARI</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D251" s="4" t="inlineStr">
         <is>
-          <t>DET -3</t>
+          <t>SEA ML</t>
         </is>
       </c>
       <c r="E251" s="7" t="n">
-        <v>-110</v>
+        <v>-225</v>
       </c>
       <c r="F251" s="8" t="n">
-        <v>0.4564</v>
+        <v>0.6056</v>
       </c>
       <c r="G251" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.6923</v>
       </c>
       <c r="H251" s="8" t="n">
-        <v>-0.05056972123582924</v>
+        <v>-0.05060085533297158</v>
       </c>
       <c r="I251" s="8" t="n">
-        <v>-0.1195538545454545</v>
+        <v>-0.1241422933333333</v>
       </c>
       <c r="J251" s="10" t="n">
         <v>0.75</v>
@@ -15217,7 +15221,7 @@
       </c>
       <c r="B252" s="5" t="inlineStr">
         <is>
-          <t>SEA @ ARI</t>
+          <t>MIA @ MIN</t>
         </is>
       </c>
       <c r="C252" s="5" t="inlineStr">
@@ -15227,28 +15231,32 @@
       </c>
       <c r="D252" s="5" t="inlineStr">
         <is>
-          <t>SEA ML</t>
+          <t>MIN ML</t>
         </is>
       </c>
       <c r="E252" s="12" t="n">
-        <v>-225</v>
+        <v>-410</v>
       </c>
       <c r="F252" s="13" t="n">
-        <v>0.6056</v>
+        <v>0.7038</v>
       </c>
       <c r="G252" s="13" t="n">
-        <v>0.6923</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="H252" s="13" t="n">
-        <v>-0.05060085533297158</v>
+        <v>-0.05065415282043377</v>
       </c>
       <c r="I252" s="13" t="n">
-        <v>-0.1241422933333333</v>
+        <v>-0.1235202234146341</v>
       </c>
       <c r="J252" s="15" t="n">
         <v>0.75</v>
       </c>
-      <c r="K252" s="5" t="inlineStr"/>
+      <c r="K252" s="5" t="inlineStr">
+        <is>
+          <t>price -410 outside the allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
@@ -15258,7 +15266,7 @@
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>MIA @ MIN</t>
+          <t>PHI @ TEN</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
@@ -15268,32 +15276,28 @@
       </c>
       <c r="D253" s="4" t="inlineStr">
         <is>
-          <t>MIN ML</t>
+          <t>PHI ML</t>
         </is>
       </c>
       <c r="E253" s="7" t="n">
-        <v>-410</v>
+        <v>-305</v>
       </c>
       <c r="F253" s="8" t="n">
-        <v>0.7038</v>
+        <v>0.658</v>
       </c>
       <c r="G253" s="8" t="n">
-        <v>0.8038999999999999</v>
+        <v>0.7531</v>
       </c>
       <c r="H253" s="8" t="n">
-        <v>-0.05065415282043377</v>
+        <v>-0.05080602646866703</v>
       </c>
       <c r="I253" s="8" t="n">
-        <v>-0.1235202234146341</v>
+        <v>-0.1251764393442623</v>
       </c>
       <c r="J253" s="10" t="n">
         <v>0.75</v>
       </c>
-      <c r="K253" s="4" t="inlineStr">
-        <is>
-          <t>price -410 outside the allowed range</t>
-        </is>
-      </c>
+      <c r="K253" s="4" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="5" t="inlineStr">
@@ -15303,7 +15307,7 @@
       </c>
       <c r="B254" s="5" t="inlineStr">
         <is>
-          <t>PHI @ TEN</t>
+          <t>LV @ LAC</t>
         </is>
       </c>
       <c r="C254" s="5" t="inlineStr">
@@ -15313,23 +15317,23 @@
       </c>
       <c r="D254" s="5" t="inlineStr">
         <is>
-          <t>PHI ML</t>
+          <t>LAC ML</t>
         </is>
       </c>
       <c r="E254" s="12" t="n">
-        <v>-305</v>
+        <v>-310</v>
       </c>
       <c r="F254" s="13" t="n">
-        <v>0.658</v>
+        <v>0.6612</v>
       </c>
       <c r="G254" s="13" t="n">
-        <v>0.7531</v>
+        <v>0.7561</v>
       </c>
       <c r="H254" s="13" t="n">
-        <v>-0.05080602646866703</v>
+        <v>-0.05084056264511968</v>
       </c>
       <c r="I254" s="13" t="n">
-        <v>-0.1251764393442623</v>
+        <v>-0.1244428451612903</v>
       </c>
       <c r="J254" s="15" t="n">
         <v>0.75</v>
@@ -15344,33 +15348,33 @@
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>LV @ LAC</t>
+          <t>MIN @ CHI</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D255" s="4" t="inlineStr">
         <is>
-          <t>LAC ML</t>
+          <t>CHI -5.5</t>
         </is>
       </c>
       <c r="E255" s="7" t="n">
-        <v>-310</v>
+        <v>-110</v>
       </c>
       <c r="F255" s="8" t="n">
-        <v>0.6612</v>
+        <v>0.4554</v>
       </c>
       <c r="G255" s="8" t="n">
-        <v>0.7561</v>
+        <v>0.5238</v>
       </c>
       <c r="H255" s="8" t="n">
-        <v>-0.05084056264511968</v>
+        <v>-0.05086881468618579</v>
       </c>
       <c r="I255" s="8" t="n">
-        <v>-0.1244428451612903</v>
+        <v>-0.1305999999999999</v>
       </c>
       <c r="J255" s="10" t="n">
         <v>0.75</v>
@@ -15385,7 +15389,7 @@
       </c>
       <c r="B256" s="5" t="inlineStr">
         <is>
-          <t>MIN @ CHI</t>
+          <t>WSH @ DAL</t>
         </is>
       </c>
       <c r="C256" s="5" t="inlineStr">
@@ -15395,23 +15399,23 @@
       </c>
       <c r="D256" s="5" t="inlineStr">
         <is>
-          <t>CHI -5.5</t>
+          <t>DAL -3.5</t>
         </is>
       </c>
       <c r="E256" s="12" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="F256" s="13" t="n">
-        <v>0.4554</v>
+        <v>0.4593</v>
       </c>
       <c r="G256" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5283</v>
       </c>
       <c r="H256" s="13" t="n">
-        <v>-0.05086881468618579</v>
+        <v>-0.05087352545864773</v>
       </c>
       <c r="I256" s="13" t="n">
-        <v>-0.1305999999999999</v>
+        <v>-0.1306107142857144</v>
       </c>
       <c r="J256" s="15" t="n">
         <v>0.75</v>
@@ -15426,33 +15430,33 @@
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>WSH @ DAL</t>
+          <t>DET @ CAR</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D257" s="4" t="inlineStr">
         <is>
-          <t>DAL -3.5</t>
+          <t>Under 47.5</t>
         </is>
       </c>
       <c r="E257" s="7" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="F257" s="8" t="n">
-        <v>0.4593</v>
+        <v>0.4545</v>
       </c>
       <c r="G257" s="8" t="n">
-        <v>0.5283</v>
+        <v>0.5238</v>
       </c>
       <c r="H257" s="8" t="n">
-        <v>-0.05087352545864773</v>
+        <v>-0.0511213305922864</v>
       </c>
       <c r="I257" s="8" t="n">
-        <v>-0.1306107142857144</v>
+        <v>-0.1323181818181818</v>
       </c>
       <c r="J257" s="10" t="n">
         <v>0.75</v>
@@ -15467,38 +15471,42 @@
       </c>
       <c r="B258" s="5" t="inlineStr">
         <is>
-          <t>DET @ CAR</t>
+          <t>ATL @ GB</t>
         </is>
       </c>
       <c r="C258" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D258" s="5" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
+          <t>GB ML</t>
         </is>
       </c>
       <c r="E258" s="12" t="n">
-        <v>-110</v>
+        <v>-375</v>
       </c>
       <c r="F258" s="13" t="n">
-        <v>0.4545</v>
+        <v>0.6879</v>
       </c>
       <c r="G258" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.7895</v>
       </c>
       <c r="H258" s="13" t="n">
-        <v>-0.0511213305922864</v>
+        <v>-0.05119165462188179</v>
       </c>
       <c r="I258" s="13" t="n">
-        <v>-0.1323181818181818</v>
+        <v>-0.1275921220000001</v>
       </c>
       <c r="J258" s="15" t="n">
         <v>0.75</v>
       </c>
-      <c r="K258" s="5" t="inlineStr"/>
+      <c r="K258" s="5" t="inlineStr">
+        <is>
+          <t>price -375 outside the allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
@@ -15508,42 +15516,38 @@
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>ATL @ GB</t>
+          <t>SEA @ ARI</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D259" s="4" t="inlineStr">
         <is>
-          <t>GB ML</t>
+          <t>SEA -4.5</t>
         </is>
       </c>
       <c r="E259" s="7" t="n">
-        <v>-375</v>
+        <v>-105</v>
       </c>
       <c r="F259" s="8" t="n">
-        <v>0.6879</v>
+        <v>0.4428</v>
       </c>
       <c r="G259" s="8" t="n">
-        <v>0.7895</v>
+        <v>0.5122</v>
       </c>
       <c r="H259" s="8" t="n">
-        <v>-0.05119165462188179</v>
+        <v>-0.05161229066891383</v>
       </c>
       <c r="I259" s="8" t="n">
-        <v>-0.1275921220000001</v>
+        <v>-0.1354857142857142</v>
       </c>
       <c r="J259" s="10" t="n">
         <v>0.75</v>
       </c>
-      <c r="K259" s="4" t="inlineStr">
-        <is>
-          <t>price -375 outside the allowed range</t>
-        </is>
-      </c>
+      <c r="K259" s="4" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="5" t="inlineStr">
@@ -15553,33 +15557,33 @@
       </c>
       <c r="B260" s="5" t="inlineStr">
         <is>
-          <t>SEA @ ARI</t>
+          <t>SEA @ WSH</t>
         </is>
       </c>
       <c r="C260" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D260" s="5" t="inlineStr">
         <is>
-          <t>SEA -4.5</t>
+          <t>SEA ML</t>
         </is>
       </c>
       <c r="E260" s="12" t="n">
-        <v>-105</v>
+        <v>-185</v>
       </c>
       <c r="F260" s="13" t="n">
-        <v>0.4428</v>
+        <v>0.5628</v>
       </c>
       <c r="G260" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.6491</v>
       </c>
       <c r="H260" s="13" t="n">
-        <v>-0.05161229066891383</v>
+        <v>-0.05173599715981957</v>
       </c>
       <c r="I260" s="13" t="n">
-        <v>-0.1354857142857142</v>
+        <v>-0.1317869297297298</v>
       </c>
       <c r="J260" s="15" t="n">
         <v>0.75</v>
@@ -15594,33 +15598,33 @@
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>SEA @ WSH</t>
+          <t>MIN @ TB</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D261" s="4" t="inlineStr">
         <is>
-          <t>SEA ML</t>
+          <t>Under 44.5</t>
         </is>
       </c>
       <c r="E261" s="7" t="n">
-        <v>-185</v>
+        <v>-110</v>
       </c>
       <c r="F261" s="8" t="n">
-        <v>0.5628</v>
+        <v>0.452</v>
       </c>
       <c r="G261" s="8" t="n">
-        <v>0.6491</v>
+        <v>0.5238</v>
       </c>
       <c r="H261" s="8" t="n">
-        <v>-0.05173599715981957</v>
+        <v>-0.05174707951799836</v>
       </c>
       <c r="I261" s="8" t="n">
-        <v>-0.1317869297297298</v>
+        <v>-0.137090909090909</v>
       </c>
       <c r="J261" s="10" t="n">
         <v>0.75</v>
@@ -15803,33 +15807,33 @@
       </c>
       <c r="B266" s="5" t="inlineStr">
         <is>
-          <t>NE @ BUF</t>
+          <t>GB @ NYJ</t>
         </is>
       </c>
       <c r="C266" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D266" s="5" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
+          <t>GB -4.5</t>
         </is>
       </c>
       <c r="E266" s="12" t="n">
-        <v>-110</v>
+        <v>-102</v>
       </c>
       <c r="F266" s="13" t="n">
-        <v>0.447</v>
+        <v>0.4316</v>
       </c>
       <c r="G266" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.505</v>
       </c>
       <c r="H266" s="13" t="n">
-        <v>-0.05271818101122103</v>
+        <v>-0.05269183534005203</v>
       </c>
       <c r="I266" s="13" t="n">
-        <v>-0.1466363636363636</v>
+        <v>-0.1452627450980393</v>
       </c>
       <c r="J266" s="15" t="n">
         <v>0.75</v>
@@ -15844,7 +15848,7 @@
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>NYJ @ CHI</t>
+          <t>NE @ BUF</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
@@ -15854,7 +15858,7 @@
       </c>
       <c r="D267" s="4" t="inlineStr">
         <is>
-          <t>Under 45.5</t>
+          <t>Over 49.5</t>
         </is>
       </c>
       <c r="E267" s="7" t="n">
@@ -15885,7 +15889,7 @@
       </c>
       <c r="B268" s="5" t="inlineStr">
         <is>
-          <t>MIA @ MIN</t>
+          <t>NYJ @ CHI</t>
         </is>
       </c>
       <c r="C268" s="5" t="inlineStr">
@@ -15895,7 +15899,7 @@
       </c>
       <c r="D268" s="5" t="inlineStr">
         <is>
-          <t>Under 43.5</t>
+          <t>Under 45.5</t>
         </is>
       </c>
       <c r="E268" s="12" t="n">
@@ -15926,33 +15930,33 @@
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>GB @ NYJ</t>
+          <t>MIA @ MIN</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D269" s="4" t="inlineStr">
         <is>
-          <t>GB -4.5</t>
+          <t>Under 43.5</t>
         </is>
       </c>
       <c r="E269" s="7" t="n">
-        <v>-102</v>
+        <v>-110</v>
       </c>
       <c r="F269" s="8" t="n">
-        <v>0.4309</v>
+        <v>0.447</v>
       </c>
       <c r="G269" s="8" t="n">
-        <v>0.505</v>
+        <v>0.5238</v>
       </c>
       <c r="H269" s="8" t="n">
-        <v>-0.05280806055542792</v>
+        <v>-0.05271818101122103</v>
       </c>
       <c r="I269" s="8" t="n">
-        <v>-0.146649019607843</v>
+        <v>-0.1466363636363636</v>
       </c>
       <c r="J269" s="10" t="n">
         <v>0.75</v>
@@ -16603,16 +16607,16 @@
         <v>-110</v>
       </c>
       <c r="F285" s="8" t="n">
-        <v>0.4255</v>
+        <v>0.4263</v>
       </c>
       <c r="G285" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H285" s="8" t="n">
-        <v>-0.05451428189255149</v>
+        <v>-0.05448531979150142</v>
       </c>
       <c r="I285" s="8" t="n">
-        <v>-0.1876818181818182</v>
+        <v>-0.1861545454545454</v>
       </c>
       <c r="J285" s="10" t="n">
         <v>0.75</v>
@@ -16709,33 +16713,33 @@
       </c>
       <c r="B288" s="5" t="inlineStr">
         <is>
-          <t>PHI @ TEN</t>
+          <t>CLE @ TB</t>
         </is>
       </c>
       <c r="C288" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D288" s="5" t="inlineStr">
         <is>
-          <t>Under 39.5</t>
+          <t>TB -8.5</t>
         </is>
       </c>
       <c r="E288" s="12" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="F288" s="13" t="n">
-        <v>0.4224</v>
+        <v>0.4257</v>
       </c>
       <c r="G288" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5283</v>
       </c>
       <c r="H288" s="13" t="n">
-        <v>-0.05461197663388877</v>
+        <v>-0.05462114125046524</v>
       </c>
       <c r="I288" s="13" t="n">
-        <v>-0.1936</v>
+        <v>-0.1942107142857142</v>
       </c>
       <c r="J288" s="15" t="n">
         <v>0.75</v>
@@ -16750,7 +16754,7 @@
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>CLE @ TB</t>
+          <t>MIA @ SF</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr">
@@ -16760,23 +16764,23 @@
       </c>
       <c r="D289" s="4" t="inlineStr">
         <is>
-          <t>TB -8.5</t>
+          <t>SF -13.5</t>
         </is>
       </c>
       <c r="E289" s="7" t="n">
-        <v>-112</v>
+        <v>-105</v>
       </c>
       <c r="F289" s="8" t="n">
-        <v>0.4257</v>
+        <v>0.4109</v>
       </c>
       <c r="G289" s="8" t="n">
-        <v>0.5283</v>
+        <v>0.5122</v>
       </c>
       <c r="H289" s="8" t="n">
-        <v>-0.05462114125046524</v>
+        <v>-0.05467461468183479</v>
       </c>
       <c r="I289" s="8" t="n">
-        <v>-0.1942107142857142</v>
+        <v>-0.1977666666666668</v>
       </c>
       <c r="J289" s="10" t="n">
         <v>0.75</v>
@@ -16791,7 +16795,7 @@
       </c>
       <c r="B290" s="5" t="inlineStr">
         <is>
-          <t>MIA @ SF</t>
+          <t>PHI @ TEN</t>
         </is>
       </c>
       <c r="C290" s="5" t="inlineStr">
@@ -16801,23 +16805,23 @@
       </c>
       <c r="D290" s="5" t="inlineStr">
         <is>
-          <t>SF -13.5</t>
+          <t>PHI -7</t>
         </is>
       </c>
       <c r="E290" s="12" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="F290" s="13" t="n">
-        <v>0.4109</v>
+        <v>0.4195</v>
       </c>
       <c r="G290" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.5238</v>
       </c>
       <c r="H290" s="13" t="n">
-        <v>-0.05467461468183479</v>
+        <v>-0.05468554925400725</v>
       </c>
       <c r="I290" s="13" t="n">
-        <v>-0.1977666666666668</v>
+        <v>-0.1885223954545455</v>
       </c>
       <c r="J290" s="15" t="n">
         <v>0.75</v>
@@ -16832,7 +16836,7 @@
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>PHI @ TEN</t>
+          <t>NYJ @ DET</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
@@ -16842,23 +16846,23 @@
       </c>
       <c r="D291" s="4" t="inlineStr">
         <is>
-          <t>PHI -7</t>
+          <t>DET -9.5</t>
         </is>
       </c>
       <c r="E291" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F291" s="8" t="n">
-        <v>0.4195</v>
+        <v>0.4183</v>
       </c>
       <c r="G291" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H291" s="8" t="n">
-        <v>-0.05468554925400725</v>
+        <v>-0.05471175994430898</v>
       </c>
       <c r="I291" s="8" t="n">
-        <v>-0.1885223954545455</v>
+        <v>-0.2014272727272727</v>
       </c>
       <c r="J291" s="10" t="n">
         <v>0.75</v>
@@ -16873,33 +16877,33 @@
       </c>
       <c r="B292" s="5" t="inlineStr">
         <is>
-          <t>NYJ @ DET</t>
+          <t>PHI @ TEN</t>
         </is>
       </c>
       <c r="C292" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D292" s="5" t="inlineStr">
         <is>
-          <t>DET -9.5</t>
+          <t>Under 39.5</t>
         </is>
       </c>
       <c r="E292" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F292" s="13" t="n">
-        <v>0.4177</v>
+        <v>0.4175</v>
       </c>
       <c r="G292" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H292" s="13" t="n">
-        <v>-0.05472403634105155</v>
+        <v>-0.05472801145277018</v>
       </c>
       <c r="I292" s="13" t="n">
-        <v>-0.2025727272727272</v>
+        <v>-0.2029545454545455</v>
       </c>
       <c r="J292" s="15" t="n">
         <v>0.75</v>
@@ -16955,33 +16959,33 @@
       </c>
       <c r="B294" s="5" t="inlineStr">
         <is>
-          <t>BAL @ DAL</t>
+          <t>ARI @ SF</t>
         </is>
       </c>
       <c r="C294" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D294" s="5" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>SF -11.5</t>
         </is>
       </c>
       <c r="E294" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F294" s="13" t="n">
-        <v>0.4127</v>
+        <v>0.411</v>
       </c>
       <c r="G294" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H294" s="13" t="n">
-        <v>-0.05480801870864256</v>
+        <v>-0.05483031147374638</v>
       </c>
       <c r="I294" s="13" t="n">
-        <v>-0.2121181818181818</v>
+        <v>-0.2153636363636364</v>
       </c>
       <c r="J294" s="15" t="n">
         <v>0.75</v>
@@ -16996,33 +17000,33 @@
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>ARI @ SF</t>
+          <t>BAL @ DAL</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D295" s="4" t="inlineStr">
         <is>
-          <t>SF -11.5</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="E295" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F295" s="8" t="n">
-        <v>0.411</v>
+        <v>0.4055</v>
       </c>
       <c r="G295" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H295" s="8" t="n">
-        <v>-0.05483031147374638</v>
+        <v>-0.05488619650201235</v>
       </c>
       <c r="I295" s="8" t="n">
-        <v>-0.2153636363636364</v>
+        <v>-0.2258636363636363</v>
       </c>
       <c r="J295" s="10" t="n">
         <v>0.75</v>
@@ -18474,7 +18478,7 @@
         </is>
       </c>
       <c r="D21" s="14" t="n">
-        <v>6.56</v>
+        <v>6.61</v>
       </c>
       <c r="E21" s="14" t="n">
         <v>-8.5</v>
@@ -18684,7 +18688,7 @@
         <v>2.5</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>48</v>
+        <v>47.7</v>
       </c>
       <c r="G27" s="16" t="n">
         <v>51.5</v>
@@ -18786,7 +18790,7 @@
         <v>-1.5</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>45.9</v>
+        <v>46.4</v>
       </c>
       <c r="G30" s="11" t="n">
         <v>44.5</v>
@@ -18922,7 +18926,7 @@
         <v>7.5</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>45.7</v>
+        <v>45.3</v>
       </c>
       <c r="G34" s="11" t="n">
         <v>44.5</v>
@@ -18984,7 +18988,7 @@
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>6.88</v>
+        <v>6.91</v>
       </c>
       <c r="E36" s="9" t="n">
         <v>-9.5</v>
@@ -19092,7 +19096,7 @@
         <v>-1.5</v>
       </c>
       <c r="F39" s="16" t="n">
-        <v>44.7</v>
+        <v>45.2</v>
       </c>
       <c r="G39" s="16" t="n">
         <v>45.5</v>
@@ -19126,7 +19130,7 @@
         <v>-7.5</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>45.4</v>
+        <v>46.5</v>
       </c>
       <c r="G40" s="11" t="n">
         <v>46.5</v>
@@ -19194,7 +19198,7 @@
         <v>-6.5</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>46.9</v>
+        <v>47.3</v>
       </c>
       <c r="G42" s="11" t="n">
         <v>47.5</v>
@@ -19494,13 +19498,13 @@
         </is>
       </c>
       <c r="D51" s="14" t="n">
-        <v>-2.11</v>
+        <v>-2.15</v>
       </c>
       <c r="E51" s="14" t="n">
         <v>4.5</v>
       </c>
       <c r="F51" s="16" t="n">
-        <v>44.7</v>
+        <v>45.8</v>
       </c>
       <c r="G51" s="16" t="n">
         <v>44.5</v>
@@ -19602,7 +19606,7 @@
         <v>7</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>42.6</v>
+        <v>42.8</v>
       </c>
       <c r="G54" s="11" t="n">
         <v>39.5</v>
@@ -19636,7 +19640,7 @@
         <v>-5.5</v>
       </c>
       <c r="F55" s="16" t="n">
-        <v>42.5</v>
+        <v>43.6</v>
       </c>
       <c r="G55" s="16" t="n">
         <v>42.5</v>
@@ -40898,7 +40902,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Knight played three offensive snaps and three special teams snaps in Sunday's 26-14 win over the Chargers.</t>
+          <t>Knight played three offensive snaps and three special-teams snaps in Sunday's 26-14 win over the Chargers.</t>
         </is>
       </c>
     </row>
@@ -41690,7 +41694,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Folk went 2 for 4 on field-goal attempts and hit his only extra-point try in Sunday's 20-13 loss to the Steelers.</t>
+          <t>Folk went 2-for-4 on field-goal attempts and hit his only extra-point try in Sunday's 20-13 loss to the Steelers.</t>
         </is>
       </c>
     </row>
@@ -41722,7 +41726,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Zaccheaus caught his sole target for five yards and returned one kick for 29 yards in the Falcons' 20-13 loss to the Steelers on Sunday.</t>
+          <t>Zaccheaus caught his sole target for five yards and returned one kickoff for 29 yards in the Falcons' 20-13 loss to the Steelers on Sunday.</t>
         </is>
       </c>
     </row>
@@ -41754,7 +41758,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Branch returned three punts for 33 yards and one kick for 30 yards in the Packers' 39-22 loss to the Vikings on Sunday.</t>
+          <t>Branch returned three punts for 33 yards and one kickoff for 30 yards in the Falcons' 20-13 loss to the Steelers on Sunday.</t>
         </is>
       </c>
     </row>
@@ -46246,17 +46250,17 @@
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>Teven Jenkins</t>
+          <t>Dylan Sampson</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
@@ -46266,7 +46270,7 @@
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>Sampson (knee) was placed on injured reserve Tuesday.</t>
         </is>
       </c>
     </row>
@@ -46278,12 +46282,12 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Parker Brailsford</t>
+          <t>Teven Jenkins</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
@@ -46310,27 +46314,27 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>Carson Schwesinger</t>
+          <t>Parker Brailsford</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>Schwesinger finished with 10 tackles (three solo), including one for a loss, in Sunday's 34-10 loss to the Jaguars.</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -46342,12 +46346,12 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Andre Szmyt</t>
+          <t>Carson Schwesinger</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
@@ -46362,7 +46366,7 @@
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>Szmyt made his only field-goal attempt and extra-point try in Sunday's 34-10 loss to the Jaguars.</t>
+          <t>Schwesinger finished with 10 tackles (three solo), including one for a loss, in Sunday's 34-10 loss to the Jaguars.</t>
         </is>
       </c>
     </row>
@@ -46374,12 +46378,12 @@
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>Raheim Sanders</t>
+          <t>Andre Szmyt</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
@@ -46394,7 +46398,7 @@
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>Sanders caught all three of his targets for 25 yards and added one rush on the ground for a yard in Sunday's 34-10 loss to the Jaguars.</t>
+          <t>Szmyt made his only field-goal attempt and extra-point try in Sunday's 34-10 loss to the Jaguars.</t>
         </is>
       </c>
     </row>
@@ -46406,12 +46410,12 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Jerry Jeudy</t>
+          <t>Raheim Sanders</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
@@ -46426,7 +46430,7 @@
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>Jeudy caught two passes on four targets for 26 yards during the Browns' 34-10 loss to the Jaguars on Sunday.</t>
+          <t>Sanders caught all three of his targets for 25 yards and added one carry for one yard in Sunday's 34-10 loss to the Jaguars. He also returned three kickoffs for 130 yards.</t>
         </is>
       </c>
     </row>
@@ -46438,27 +46442,27 @@
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>Dylan Sampson</t>
+          <t>Jerry Jeudy</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>Out</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>Coach Todd Monken said Monday the team is still evaluating the severity of Sampson's knee injury, Daniel Oyefusi of ESPN.com reports.</t>
+          <t>Jeudy caught two passes (on four targets) for 26 yards during the Browns' 34-10 loss to the Jaguars on Sunday.</t>
         </is>
       </c>
     </row>
@@ -47302,7 +47306,7 @@
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>Coach Brian Schottenheimer said Monday that Overshown is expected to miss 1-2 weeks due to the hamstring injury he sustained during Sunday's loss against the Giants, Andrew Siciliano of NFL Network reports.</t>
+          <t>Coach Brian Schottenheimer said Monday that Overshown is expected to miss 1-to-2 weeks due to the hamstring injury he sustained during Sunday's loss against the Giants, Andrew Siciliano of NFL Network reports.</t>
         </is>
       </c>
     </row>
@@ -48642,7 +48646,7 @@
       </c>
       <c r="F256" s="5" t="inlineStr">
         <is>
-          <t>Saylors made one tackle and returned two kicks for 25 yards in Sunday's 31-30 overtime win against the Saints.</t>
+          <t>Saylors made one special-teams tackle and returned two kickoffs for 25 yards in Sunday's 31-30 overtime win against the Saints.</t>
         </is>
       </c>
     </row>
@@ -49554,7 +49558,7 @@
       </c>
       <c r="F285" s="4" t="inlineStr">
         <is>
-          <t>Johnson returned two kicks for 52 yards in Sunday's 39-22 loss to the Vikings.</t>
+          <t>Johnson returned two kickoffs for 52 yards in Sunday's 39-22 loss to the Vikings.</t>
         </is>
       </c>
     </row>
@@ -50990,7 +50994,7 @@
       </c>
       <c r="F331" s="4" t="inlineStr">
         <is>
-          <t>Shrader converted his only field-goal attempts and two of his three extra-point tries during Indianapolis' loss to the Ravens on Sunday.</t>
+          <t>Shrader converted his only field-goal attempt and two of his three extra-point tries during Indianapolis' loss to the Ravens on Sunday.</t>
         </is>
       </c>
     </row>
@@ -51054,7 +51058,7 @@
       </c>
       <c r="F333" s="4" t="inlineStr">
         <is>
-          <t>McGowan caught his only target for no gain and notched 164 yards on five kick returns during Sunday's 41-23 loss to the Ravens.</t>
+          <t>McGowan caught his only target for no gain and notched 164 yards on five kickoff returns during Sunday's 41-23 loss to the Ravens.</t>
         </is>
       </c>
     </row>
@@ -51738,7 +51742,7 @@
       </c>
       <c r="F355" s="4" t="inlineStr">
         <is>
-          <t>Williams didn't record any offensive stats during</t>
+          <t>Williams didn't record any offensive stats during Sunday's 34-10 win over the Browns.</t>
         </is>
       </c>
     </row>
@@ -52502,27 +52506,27 @@
       </c>
       <c r="B380" s="5" t="inlineStr">
         <is>
-          <t>Josh Simmons</t>
+          <t>Emmett Johnson</t>
         </is>
       </c>
       <c r="C380" s="5" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D380" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E380" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F380" s="5" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>Johnson rushed eight times for 24 yards in the Chiefs' 31-10 win over the Broncos on Monday night. He added two catches for 44 yards on two targets.</t>
         </is>
       </c>
     </row>
@@ -52534,12 +52538,12 @@
       </c>
       <c r="B381" s="4" t="inlineStr">
         <is>
-          <t>Chamarri Conner</t>
+          <t>Josh Simmons</t>
         </is>
       </c>
       <c r="C381" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>OT</t>
         </is>
       </c>
       <c r="D381" s="4" t="inlineStr">
@@ -52566,25 +52570,29 @@
       </c>
       <c r="B382" s="5" t="inlineStr">
         <is>
-          <t>Jared Wiley</t>
+          <t>Chamarri Conner</t>
         </is>
       </c>
       <c r="C382" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D382" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E382" s="5" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F382" s="5" t="inlineStr"/>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F382" s="5" t="inlineStr">
+        <is>
+          <t>questionable</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="4" t="inlineStr">
@@ -52594,12 +52602,12 @@
       </c>
       <c r="B383" s="4" t="inlineStr">
         <is>
-          <t>Diego Pounds</t>
+          <t>Jared Wiley</t>
         </is>
       </c>
       <c r="C383" s="4" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D383" s="4" t="inlineStr">
@@ -52622,12 +52630,12 @@
       </c>
       <c r="B384" s="5" t="inlineStr">
         <is>
-          <t>Bryson Eason</t>
+          <t>Diego Pounds</t>
         </is>
       </c>
       <c r="C384" s="5" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>OT</t>
         </is>
       </c>
       <c r="D384" s="5" t="inlineStr">
@@ -52650,12 +52658,12 @@
       </c>
       <c r="B385" s="4" t="inlineStr">
         <is>
-          <t>Jack Pyburn</t>
+          <t>Bryson Eason</t>
         </is>
       </c>
       <c r="C385" s="4" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D385" s="4" t="inlineStr">
@@ -52678,12 +52686,12 @@
       </c>
       <c r="B386" s="5" t="inlineStr">
         <is>
-          <t>Xavier Worthy</t>
+          <t>Jack Pyburn</t>
         </is>
       </c>
       <c r="C386" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D386" s="5" t="inlineStr">
@@ -52696,11 +52704,7 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F386" s="5" t="inlineStr">
-        <is>
-          <t>Worthy secured three of six targets for 18 yards in the Chiefs' 31-10 win over the Broncos on Monday night.</t>
-        </is>
-      </c>
+      <c r="F386" s="5" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" s="4" t="inlineStr">
@@ -52710,12 +52714,12 @@
       </c>
       <c r="B387" s="4" t="inlineStr">
         <is>
-          <t>Travis Kelce</t>
+          <t>Xavier Worthy</t>
         </is>
       </c>
       <c r="C387" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D387" s="4" t="inlineStr">
@@ -52730,7 +52734,7 @@
       </c>
       <c r="F387" s="4" t="inlineStr">
         <is>
-          <t>Kelce brought in three of five targets for 71 yards in the Chiefs' 31-10 win over the Broncos on Monday night.</t>
+          <t>Worthy secured three of six targets for 18 yards in the Chiefs' 31-10 win over the Broncos on Monday night.</t>
         </is>
       </c>
     </row>
@@ -52742,12 +52746,12 @@
       </c>
       <c r="B388" s="5" t="inlineStr">
         <is>
-          <t>Patrick Mahomes</t>
+          <t>Travis Kelce</t>
         </is>
       </c>
       <c r="C388" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D388" s="5" t="inlineStr">
@@ -52762,7 +52766,7 @@
       </c>
       <c r="F388" s="5" t="inlineStr">
         <is>
-          <t>Mahomes completed 15 of 27 passes for 184 yards with two touchdowns and one interception while adding seven rushes for 23 yards and another score in the Chiefs' 31-10 win over the Broncos on Monday night. He also recovered two fumbles.</t>
+          <t>Kelce brought in three of five targets for 71 yards in the Chiefs' 31-10 win over the Broncos on Monday night.</t>
         </is>
       </c>
     </row>
@@ -52774,12 +52778,12 @@
       </c>
       <c r="B389" s="4" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Patrick Mahomes</t>
         </is>
       </c>
       <c r="C389" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D389" s="4" t="inlineStr">
@@ -52794,7 +52798,7 @@
       </c>
       <c r="F389" s="4" t="inlineStr">
         <is>
-          <t>Rice brought in both targets for 19 yards and a touchdown in the Chiefs' 31-10 win over the Broncos on Monday night.</t>
+          <t>Mahomes completed 15 of 27 passes for 184 yards with two touchdowns and one interception while adding seven rushes for 23 yards and another score in the Chiefs' 31-10 win over the Broncos on Monday night. He also recovered two fumbles.</t>
         </is>
       </c>
     </row>
@@ -52806,12 +52810,12 @@
       </c>
       <c r="B390" s="5" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="C390" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D390" s="5" t="inlineStr">
@@ -52826,7 +52830,7 @@
       </c>
       <c r="F390" s="5" t="inlineStr">
         <is>
-          <t>Walker rushed 23 times for 173 yards and a touchdown and brought in three of six targets for 18 yards and another score in the Chiefs' 31-10 win over the Broncos on Monday night.</t>
+          <t>Rice brought in both targets for 19 yards and a touchdown in the Chiefs' 31-10 win over the Broncos on Monday night.</t>
         </is>
       </c>
     </row>
@@ -52838,27 +52842,27 @@
       </c>
       <c r="B391" s="4" t="inlineStr">
         <is>
-          <t>Cooper McDonald</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C391" s="4" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D391" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E391" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F391" s="4" t="inlineStr">
         <is>
-          <t>McDonald (knee) has been ruled out for the remainder of Sunday's game against the Broncos.</t>
+          <t>Walker rushed 23 times for 173 yards and a touchdown and brought in three of six targets for 18 yards and another score in the Chiefs' 31-10 win over the Broncos on Monday night.</t>
         </is>
       </c>
     </row>
@@ -52870,12 +52874,12 @@
       </c>
       <c r="B392" s="5" t="inlineStr">
         <is>
-          <t>Mansoor Delane</t>
+          <t>Cooper McDonald</t>
         </is>
       </c>
       <c r="C392" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D392" s="5" t="inlineStr">
@@ -52890,7 +52894,7 @@
       </c>
       <c r="F392" s="5" t="inlineStr">
         <is>
-          <t>Delane (shoulder) has been ruled out for the remainder of Monday night's game against the Broncos.</t>
+          <t>McDonald (knee) has been ruled out for the remainder of Monday night's game against the Broncos.</t>
         </is>
       </c>
     </row>
@@ -52902,27 +52906,27 @@
       </c>
       <c r="B393" s="4" t="inlineStr">
         <is>
-          <t>Garrett Nussmeier</t>
+          <t>Mansoor Delane</t>
         </is>
       </c>
       <c r="C393" s="4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D393" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E393" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F393" s="4" t="inlineStr">
         <is>
-          <t>Nussmeier (coach's decision) is inactive as the emergency third quarterback for Monday night's game against the Broncos.</t>
+          <t>Delane (shoulder) has been ruled out for the remainder of Monday night's game against the Broncos.</t>
         </is>
       </c>
     </row>
@@ -52934,12 +52938,12 @@
       </c>
       <c r="B394" s="5" t="inlineStr">
         <is>
-          <t>Ben VanSumeren</t>
+          <t>Garrett Nussmeier</t>
         </is>
       </c>
       <c r="C394" s="5" t="inlineStr">
         <is>
-          <t>FB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D394" s="5" t="inlineStr">
@@ -52954,7 +52958,7 @@
       </c>
       <c r="F394" s="5" t="inlineStr">
         <is>
-          <t>The Chiefs elevated VanSumeren from the practice squad ahead of Monday's game against the Broncos.</t>
+          <t>Nussmeier (coach's decision) is inactive as the emergency third quarterback for Monday night's game against the Broncos.</t>
         </is>
       </c>
     </row>
@@ -52966,12 +52970,12 @@
       </c>
       <c r="B395" s="4" t="inlineStr">
         <is>
-          <t>Chris Jones</t>
+          <t>Ben VanSumeren</t>
         </is>
       </c>
       <c r="C395" s="4" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="D395" s="4" t="inlineStr">
@@ -52986,7 +52990,7 @@
       </c>
       <c r="F395" s="4" t="inlineStr">
         <is>
-          <t>Jones (calf) does not have an injury designation ahead of Monday night's game against the Broncos.</t>
+          <t>The Chiefs elevated VanSumeren from the practice squad ahead of Monday's game against the Broncos.</t>
         </is>
       </c>
     </row>
@@ -52998,12 +53002,12 @@
       </c>
       <c r="B396" s="5" t="inlineStr">
         <is>
-          <t>Ashton Gillotte</t>
+          <t>Chris Jones</t>
         </is>
       </c>
       <c r="C396" s="5" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D396" s="5" t="inlineStr">
@@ -53018,7 +53022,7 @@
       </c>
       <c r="F396" s="5" t="inlineStr">
         <is>
-          <t>Gillotte (foot) was a full participant in practice Thursday.</t>
+          <t>Jones (calf) does not have an injury designation ahead of Monday night's game against the Broncos.</t>
         </is>
       </c>
     </row>
@@ -53030,12 +53034,12 @@
       </c>
       <c r="B397" s="4" t="inlineStr">
         <is>
-          <t>Trey Smith</t>
+          <t>Ashton Gillotte</t>
         </is>
       </c>
       <c r="C397" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D397" s="4" t="inlineStr">
@@ -53050,7 +53054,7 @@
       </c>
       <c r="F397" s="4" t="inlineStr">
         <is>
-          <t>Smith (hip) was a full participant in practice Thursday.</t>
+          <t>Gillotte (foot) was a full participant in practice Thursday.</t>
         </is>
       </c>
     </row>
@@ -53062,12 +53066,12 @@
       </c>
       <c r="B398" s="5" t="inlineStr">
         <is>
-          <t>R Mason Thomas</t>
+          <t>Trey Smith</t>
         </is>
       </c>
       <c r="C398" s="5" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D398" s="5" t="inlineStr">
@@ -53082,7 +53086,7 @@
       </c>
       <c r="F398" s="5" t="inlineStr">
         <is>
-          <t>Thomas (hamstring) was a full participant in practice Thursday.</t>
+          <t>Smith (hip) was a full participant in practice Thursday.</t>
         </is>
       </c>
     </row>
@@ -53094,12 +53098,12 @@
       </c>
       <c r="B399" s="4" t="inlineStr">
         <is>
-          <t>L'Jarius Sneed</t>
+          <t>R Mason Thomas</t>
         </is>
       </c>
       <c r="C399" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D399" s="4" t="inlineStr">
@@ -53114,7 +53118,7 @@
       </c>
       <c r="F399" s="4" t="inlineStr">
         <is>
-          <t>Sneed (knee) was a full participant in practice Thursday.</t>
+          <t>Thomas (hamstring) was a full participant in practice Thursday.</t>
         </is>
       </c>
     </row>
@@ -53126,12 +53130,12 @@
       </c>
       <c r="B400" s="5" t="inlineStr">
         <is>
-          <t>Drue Tranquill</t>
+          <t>L'Jarius Sneed</t>
         </is>
       </c>
       <c r="C400" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D400" s="5" t="inlineStr">
@@ -53146,7 +53150,7 @@
       </c>
       <c r="F400" s="5" t="inlineStr">
         <is>
-          <t>Tranquill (back) did not appear on Kansas City's injury report Thursday.</t>
+          <t>Sneed (knee) was a full participant in practice Thursday.</t>
         </is>
       </c>
     </row>
@@ -53158,12 +53162,12 @@
       </c>
       <c r="B401" s="4" t="inlineStr">
         <is>
-          <t>Alohi Gilman</t>
+          <t>Drue Tranquill</t>
         </is>
       </c>
       <c r="C401" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D401" s="4" t="inlineStr">
@@ -53178,7 +53182,7 @@
       </c>
       <c r="F401" s="4" t="inlineStr">
         <is>
-          <t>Gilman (back) is not on the Chiefs' Thursday injury report ahead of the team's Monday night Week 1 clash with the Broncos.</t>
+          <t>Tranquill (back) did not appear on Kansas City's injury report Thursday.</t>
         </is>
       </c>
     </row>
@@ -53190,12 +53194,12 @@
       </c>
       <c r="B402" s="5" t="inlineStr">
         <is>
-          <t>Cyrus Allen</t>
+          <t>Alohi Gilman</t>
         </is>
       </c>
       <c r="C402" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D402" s="5" t="inlineStr">
@@ -53210,7 +53214,7 @@
       </c>
       <c r="F402" s="5" t="inlineStr">
         <is>
-          <t>Allen is listed as a backup receiver on Kansas City's unofficial depth chart ahead of Monday's season opener versus the Broncos, Charles Goldsmith of AtoZSports.com reports.</t>
+          <t>Gilman (back) is not on the Chiefs' Thursday injury report ahead of the team's Monday night Week 1 clash with the Broncos.</t>
         </is>
       </c>
     </row>
@@ -53222,12 +53226,12 @@
       </c>
       <c r="B403" s="4" t="inlineStr">
         <is>
-          <t>Brashard Smith</t>
+          <t>Cyrus Allen</t>
         </is>
       </c>
       <c r="C403" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D403" s="4" t="inlineStr">
@@ -53242,7 +53246,7 @@
       </c>
       <c r="F403" s="4" t="inlineStr">
         <is>
-          <t>Smith is the third and final running back on the Chiefs' 53-man roster for the 2026 regular season, Matt McMullen of the team's official site reports.</t>
+          <t>Allen is listed as a backup receiver on Kansas City's unofficial depth chart ahead of Monday's season opener versus the Broncos, Charles Goldsmith of AtoZSports.com reports.</t>
         </is>
       </c>
     </row>
@@ -53254,7 +53258,7 @@
       </c>
       <c r="B404" s="5" t="inlineStr">
         <is>
-          <t>Emmett Johnson</t>
+          <t>Brashard Smith</t>
         </is>
       </c>
       <c r="C404" s="5" t="inlineStr">
@@ -53274,7 +53278,7 @@
       </c>
       <c r="F404" s="5" t="inlineStr">
         <is>
-          <t>Johnson is in line to be Kenneth Walker's backup for the Chiefs this season.</t>
+          <t>Smith is the third and final running back on the Chiefs' 53-man roster for the 2026 regular season, Matt McMullen of the team's official site reports.</t>
         </is>
       </c>
     </row>
@@ -53306,7 +53310,7 @@
       </c>
       <c r="F405" s="4" t="inlineStr">
         <is>
-          <t>Laube recorded 2 fair catches on punts, two kick returns for 95 yards and two tackles during Sunday's 27-13 win versus the Dolphins.</t>
+          <t>Laube recorded two fair catches on punts, two kickoff returns for 95 yards and two tackles during Sunday's 27-13 win versus the Dolphins.</t>
         </is>
       </c>
     </row>
@@ -53338,7 +53342,7 @@
       </c>
       <c r="F406" s="5" t="inlineStr">
         <is>
-          <t>Thomas played 31 offensive snaps in Sunday's 27-13 win over the Dolphins.</t>
+          <t>Thomas played 31 offensive snaps but did not record any stats in Sunday's 27-13 win over the Dolphins.</t>
         </is>
       </c>
     </row>
@@ -53402,7 +53406,7 @@
       </c>
       <c r="F408" s="5" t="inlineStr">
         <is>
-          <t>Benson caught one pass on two targets for six yards while taking his lone carry for minus-eight yards during the Raiders' 27-13 win over the Dolphins on Sunday. He also returned two punts for 35 yards.</t>
+          <t>Benson caught one pass (on two targets) for six yards while taking his lone carry for minus-8 yards during the Raiders' 27-13 win over the Dolphins on Sunday. He also returned two punts for 35 yards.</t>
         </is>
       </c>
     </row>
@@ -53434,7 +53438,7 @@
       </c>
       <c r="F409" s="4" t="inlineStr">
         <is>
-          <t>Nailor caught three passes on five targets for 27 yards during the Raiders' 27-13 win over the Dolphins on Sunday.</t>
+          <t>Nailor caught three passes (on five targets) for 27 yards during the Raiders' 27-13 win over the Dolphins on Sunday.</t>
         </is>
       </c>
     </row>
@@ -54118,7 +54122,7 @@
       </c>
       <c r="F431" s="4" t="inlineStr">
         <is>
-          <t>Lambert-Smith (hamstring) will miss some time after exiting last Sunday's game against the Cardinals early, Alex Insdorf of BoltBeat.com reports.</t>
+          <t>Lambert-Smith (hamstring) will miss some time after exiting Sunday's game against the Cardinals early, Alex Insdorf of BoltBeat.com reports.</t>
         </is>
       </c>
     </row>
@@ -54214,7 +54218,7 @@
       </c>
       <c r="F434" s="5" t="inlineStr">
         <is>
-          <t>Vidal played five snaps (four on offense, one on special teams) and didn't show up on the box score otherwise during then Chargers' 26-14 loss to the Cardinals on Sunday.</t>
+          <t>Vidal played five snaps (four on offense, one on special teams) and didn't show up on the box score otherwise during the Chargers' 26-14 loss to the Cardinals on Sunday.</t>
         </is>
       </c>
     </row>
@@ -54870,7 +54874,7 @@
       </c>
       <c r="F455" s="4" t="inlineStr">
         <is>
-          <t>Speights is dealing with a hip pointer coming out of the Rams' season-opening loss to the 49ers on Thursday, Stu Jackson of the team's official site reports.</t>
+          <t>Speights is dealing with a hip pointer coming out of the Rams' Week 1 loss to the 49ers, Stu Jackson of the team's official site reports.</t>
         </is>
       </c>
     </row>
@@ -54902,7 +54906,7 @@
       </c>
       <c r="F456" s="5" t="inlineStr">
         <is>
-          <t>Landman (shoulder/thumb) is expected to be ready for Monday night's game against the Giants, Rick Stroud of the Tampa Bay Times reports.</t>
+          <t>Landman (shoulder/thumb) is expected to be ready for next Monday night's game against the Giants, Rick Stroud of the Tampa Bay Times reports.</t>
         </is>
       </c>
     </row>
@@ -54966,7 +54970,7 @@
       </c>
       <c r="F458" s="5" t="inlineStr">
         <is>
-          <t>Allen (head) returned to the Week 1 contest against the 49ers, Stu Jackson of the Rams' official site reports.</t>
+          <t>Allen (head) was able to finish the Week 1 loss to the 49ers after being evaluated for a concussion, Stu Jackson of the Rams' official site reports.</t>
         </is>
       </c>
     </row>
@@ -55650,7 +55654,7 @@
       </c>
       <c r="F480" s="5" t="inlineStr">
         <is>
-          <t>Patterson converted two of his three field-goal attempts and both of his extra point tries during Miami's loss to the Raiders on Sunday.</t>
+          <t>Patterson converted two of his three field-goal attempts and both of his extra-point tries during Miami's loss to the Raiders on Sunday.</t>
         </is>
       </c>
     </row>
@@ -55810,7 +55814,7 @@
       </c>
       <c r="F485" s="4" t="inlineStr">
         <is>
-          <t>Coleman failed to bring in his two targets during Sunday's 27-13 loss to Las Vegas.</t>
+          <t>Coleman failed to bring in either of his two targets during Sunday's 27-13 loss to Las Vegas.</t>
         </is>
       </c>
     </row>
@@ -55842,7 +55846,7 @@
       </c>
       <c r="F486" s="5" t="inlineStr">
         <is>
-          <t>Bell caught one pass on two targets for 25 yards during the Dolphins' 27-13 loss to the Raiders on Sunday.</t>
+          <t>Bell caught one pass (on two targets) for 25 yards during the Dolphins' 27-13 loss to the Raiders on Sunday.</t>
         </is>
       </c>
     </row>
@@ -56470,7 +56474,7 @@
       </c>
       <c r="F506" s="5" t="inlineStr">
         <is>
-          <t>Oliver logged two catches on four targets for 22 yards during the Vikings' 39-22 win over the Packers on Sunday.</t>
+          <t>Oliver logged two catches (on four targets) for 22 yards during the Vikings' 39-22 win over the Packers on Sunday.</t>
         </is>
       </c>
     </row>
@@ -59538,17 +59542,17 @@
       </c>
       <c r="B605" s="4" t="inlineStr">
         <is>
-          <t>Kene Nwangwu</t>
+          <t>Minkah Fitzpatrick</t>
         </is>
       </c>
       <c r="C605" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D605" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Doubtful</t>
         </is>
       </c>
       <c r="E605" s="4" t="inlineStr">
@@ -59558,7 +59562,7 @@
       </c>
       <c r="F605" s="4" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>doubtful</t>
         </is>
       </c>
     </row>
@@ -59570,12 +59574,12 @@
       </c>
       <c r="B606" s="5" t="inlineStr">
         <is>
-          <t>Joseph Ossai</t>
+          <t>Kene Nwangwu</t>
         </is>
       </c>
       <c r="C606" s="5" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D606" s="5" t="inlineStr">
@@ -59585,7 +59589,7 @@
       </c>
       <c r="E606" s="5" t="inlineStr">
         <is>
-          <t>Plantar Fasciitis</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F606" s="5" t="inlineStr">
@@ -59602,12 +59606,12 @@
       </c>
       <c r="B607" s="4" t="inlineStr">
         <is>
-          <t>D'Angelo Ponds</t>
+          <t>Joseph Ossai</t>
         </is>
       </c>
       <c r="C607" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D607" s="4" t="inlineStr">
@@ -59617,7 +59621,7 @@
       </c>
       <c r="E607" s="4" t="inlineStr">
         <is>
-          <t>Strain</t>
+          <t>Plantar Fasciitis</t>
         </is>
       </c>
       <c r="F607" s="4" t="inlineStr">
@@ -59634,12 +59638,12 @@
       </c>
       <c r="B608" s="5" t="inlineStr">
         <is>
-          <t>Omar Cooper Jr.</t>
+          <t>D'Angelo Ponds</t>
         </is>
       </c>
       <c r="C608" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D608" s="5" t="inlineStr">
@@ -59649,12 +59653,12 @@
       </c>
       <c r="E608" s="5" t="inlineStr">
         <is>
-          <t>Sprain</t>
+          <t>Strain</t>
         </is>
       </c>
       <c r="F608" s="5" t="inlineStr">
         <is>
-          <t>Cooper (ankle) is "week-to-week," and the hope is he returns "within the next four weeks," Ian Rapoport of NFL Network reports.</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -59666,27 +59670,27 @@
       </c>
       <c r="B609" s="4" t="inlineStr">
         <is>
-          <t>Jason Sanders</t>
+          <t>Omar Cooper Jr.</t>
         </is>
       </c>
       <c r="C609" s="4" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D609" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E609" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Sprain</t>
         </is>
       </c>
       <c r="F609" s="4" t="inlineStr">
         <is>
-          <t>Sanders reverted to the Jets' practice squad Monday, per the NFL's transaction log.</t>
+          <t>Cooper (ankle) is "week-to-week," and the hope is he returns "within the next four weeks," Ian Rapoport of NFL Network reports.</t>
         </is>
       </c>
     </row>
@@ -59698,12 +59702,12 @@
       </c>
       <c r="B610" s="5" t="inlineStr">
         <is>
-          <t>Isaiah Davis</t>
+          <t>Jason Sanders</t>
         </is>
       </c>
       <c r="C610" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D610" s="5" t="inlineStr">
@@ -59718,7 +59722,7 @@
       </c>
       <c r="F610" s="5" t="inlineStr">
         <is>
-          <t>Davis didn't have any output in the box score during the Jets' win over the Titans on Sunday.</t>
+          <t>Sanders reverted to the Jets' practice squad Monday, per the NFL's transaction log.</t>
         </is>
       </c>
     </row>
@@ -59730,12 +59734,12 @@
       </c>
       <c r="B611" s="4" t="inlineStr">
         <is>
-          <t>Jeremy Ruckert</t>
+          <t>Isaiah Davis</t>
         </is>
       </c>
       <c r="C611" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D611" s="4" t="inlineStr">
@@ -59750,7 +59754,7 @@
       </c>
       <c r="F611" s="4" t="inlineStr">
         <is>
-          <t>Ruckert played 29 offensive snaps, catching his sole target for four yards in Sunday's 23-10 win over the Titans.</t>
+          <t>Davis didn't have any output in the box score during the Jets' win over the Titans on Sunday.</t>
         </is>
       </c>
     </row>
@@ -59762,7 +59766,7 @@
       </c>
       <c r="B612" s="5" t="inlineStr">
         <is>
-          <t>Mason Taylor</t>
+          <t>Jeremy Ruckert</t>
         </is>
       </c>
       <c r="C612" s="5" t="inlineStr">
@@ -59782,7 +59786,7 @@
       </c>
       <c r="F612" s="5" t="inlineStr">
         <is>
-          <t>Taylor caught two of three targets for minus-2 yards in the Jets' 23-10 win over the Titans on Sunday.</t>
+          <t>Ruckert played 29 offensive snaps, catching his sole target for four yards in Sunday's 23-10 win over the Titans.</t>
         </is>
       </c>
     </row>
@@ -59794,12 +59798,12 @@
       </c>
       <c r="B613" s="4" t="inlineStr">
         <is>
-          <t>Adonai Mitchell</t>
+          <t>Mason Taylor</t>
         </is>
       </c>
       <c r="C613" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D613" s="4" t="inlineStr">
@@ -59814,7 +59818,7 @@
       </c>
       <c r="F613" s="4" t="inlineStr">
         <is>
-          <t>Mitchell caught all three of his passes for 60 yards during the Jets' 23-10 win over the Titans on Sunday.</t>
+          <t>Taylor caught two of three targets for minus-2 yards in the Jets' 23-10 win over the Titans on Sunday.</t>
         </is>
       </c>
     </row>
@@ -59826,7 +59830,7 @@
       </c>
       <c r="B614" s="5" t="inlineStr">
         <is>
-          <t>Isaiah Williams</t>
+          <t>Adonai Mitchell</t>
         </is>
       </c>
       <c r="C614" s="5" t="inlineStr">
@@ -59846,7 +59850,7 @@
       </c>
       <c r="F614" s="5" t="inlineStr">
         <is>
-          <t>Williams caught his lone target for seven yards in Sunday's 23-10 win over the Titans.</t>
+          <t>Mitchell caught all three of his passes for 60 yards during the Jets' 23-10 win over the Titans on Sunday.</t>
         </is>
       </c>
     </row>
@@ -59858,12 +59862,12 @@
       </c>
       <c r="B615" s="4" t="inlineStr">
         <is>
-          <t>Braelon Allen</t>
+          <t>Isaiah Williams</t>
         </is>
       </c>
       <c r="C615" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D615" s="4" t="inlineStr">
@@ -59878,7 +59882,7 @@
       </c>
       <c r="F615" s="4" t="inlineStr">
         <is>
-          <t>Allen rushed 10 times for 40 yards in the Jets' 23-10 win over the Titans on Sunday.</t>
+          <t>Williams caught his lone target for seven yards in Sunday's 23-10 win over the Titans.</t>
         </is>
       </c>
     </row>
@@ -59890,12 +59894,12 @@
       </c>
       <c r="B616" s="5" t="inlineStr">
         <is>
-          <t>Trevin Wallace</t>
+          <t>Braelon Allen</t>
         </is>
       </c>
       <c r="C616" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D616" s="5" t="inlineStr">
@@ -59908,7 +59912,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F616" s="5" t="inlineStr"/>
+      <c r="F616" s="5" t="inlineStr">
+        <is>
+          <t>Allen rushed 10 times for 40 yards in the Jets' 23-10 win over the Titans on Sunday.</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" s="4" t="inlineStr">
@@ -59918,12 +59926,12 @@
       </c>
       <c r="B617" s="4" t="inlineStr">
         <is>
-          <t>Geno Smith</t>
+          <t>Trevin Wallace</t>
         </is>
       </c>
       <c r="C617" s="4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D617" s="4" t="inlineStr">
@@ -59936,11 +59944,7 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F617" s="4" t="inlineStr">
-        <is>
-          <t>Smith completed 19 of 24 passes for 215 yards while rushing six times for seven yards in Sunday's 23-10 win over the Titans.</t>
-        </is>
-      </c>
+      <c r="F617" s="4" t="inlineStr"/>
     </row>
     <row r="618">
       <c r="A618" s="5" t="inlineStr">
@@ -59950,12 +59954,12 @@
       </c>
       <c r="B618" s="5" t="inlineStr">
         <is>
-          <t>Kenyon Sadiq</t>
+          <t>Geno Smith</t>
         </is>
       </c>
       <c r="C618" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D618" s="5" t="inlineStr">
@@ -59970,7 +59974,7 @@
       </c>
       <c r="F618" s="5" t="inlineStr">
         <is>
-          <t>Sadiq caught all three of his targets for 31 yards in Sunday's 23-10 win over the Titans. He added one rush for a three-yard touchdown.</t>
+          <t>Smith completed 19 of 24 passes for 215 yards while rushing six times for seven yards in Sunday's 23-10 win over the Titans.</t>
         </is>
       </c>
     </row>
@@ -59982,12 +59986,12 @@
       </c>
       <c r="B619" s="4" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Kenyon Sadiq</t>
         </is>
       </c>
       <c r="C619" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D619" s="4" t="inlineStr">
@@ -60002,7 +60006,7 @@
       </c>
       <c r="F619" s="4" t="inlineStr">
         <is>
-          <t>Wilson caught six of seven targets for 79 yards in Sunday's 23-10 win over the Titans.</t>
+          <t>Sadiq caught all three of his targets for 31 yards in Sunday's 23-10 win over the Titans. He added one rush for a three-yard touchdown.</t>
         </is>
       </c>
     </row>
@@ -60014,12 +60018,12 @@
       </c>
       <c r="B620" s="5" t="inlineStr">
         <is>
-          <t>Breece Hall</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="C620" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D620" s="5" t="inlineStr">
@@ -60034,7 +60038,7 @@
       </c>
       <c r="F620" s="5" t="inlineStr">
         <is>
-          <t>Hall rushed 22 times for 102 yards and a touchdown while catching both of his targets for 16 yards in Sunday's 23-10 win over the Titans.</t>
+          <t>Wilson caught six of seven targets for 79 yards in Sunday's 23-10 win over the Titans.</t>
         </is>
       </c>
     </row>
@@ -60046,12 +60050,12 @@
       </c>
       <c r="B621" s="4" t="inlineStr">
         <is>
-          <t>Jarvis Brownlee Jr.</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="C621" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D621" s="4" t="inlineStr">
@@ -60066,7 +60070,7 @@
       </c>
       <c r="F621" s="4" t="inlineStr">
         <is>
-          <t>Brownlee (calf) has been cleared to return to Sunday's game against the Titans, Brian Costello of the New York Post reports.</t>
+          <t>Hall rushed 22 times for 102 yards and a touchdown while catching both of his targets for 16 yards in Sunday's 23-10 win over the Titans.</t>
         </is>
       </c>
     </row>
@@ -60078,27 +60082,27 @@
       </c>
       <c r="B622" s="5" t="inlineStr">
         <is>
-          <t>Minkah Fitzpatrick</t>
+          <t>Jarvis Brownlee Jr.</t>
         </is>
       </c>
       <c r="C622" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D622" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E622" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F622" s="5" t="inlineStr">
         <is>
-          <t>Fitzpatrick (groin) is now doubtful to return to Sunday's game against the Titans, Antwan V. Staley of the New York Daily News reports.</t>
+          <t>Brownlee (calf) has been cleared to return to Sunday's game against the Titans, Brian Costello of the New York Post reports.</t>
         </is>
       </c>
     </row>
@@ -60514,7 +60518,7 @@
       </c>
       <c r="F635" s="4" t="inlineStr">
         <is>
-          <t>Brown was active, but did not play in the Eagles' 24-22 win over the Commanders on Sunday.</t>
+          <t>Brown was active but did not play in the Eagles' 24-22 win over the Commanders on Sunday.</t>
         </is>
       </c>
     </row>
@@ -60600,7 +60604,7 @@
       </c>
       <c r="D638" s="5" t="inlineStr">
         <is>
-          <t>Out</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E638" s="5" t="inlineStr">
@@ -63602,7 +63606,7 @@
       </c>
       <c r="F733" s="4" t="inlineStr">
         <is>
-          <t>Parrish (back) suffered a back sprain in last Sunday's 33-27 loss to the Bengals, Brianna Dix of the Buccaneers' official site reports.</t>
+          <t>Parrish suffered a back sprain in Sunday's 33-27 loss to the Bengals, Brianna Dix of the Buccaneers' official site reports.</t>
         </is>
       </c>
     </row>
@@ -63634,7 +63638,7 @@
       </c>
       <c r="F734" s="5" t="inlineStr">
         <is>
-          <t>Trotter produced 11 tackles (four solo), including 1.0 sacks and two tackles for loss, adding a pass defensed for a 38-yard pick-six during Sunday's 33-27 loss to the Bengals.</t>
+          <t>Trotter produced 11 tackles (four solo), including 1.0 sacks and two total tackles for loss, and added a pass defensed for a 38-yard pick-six during Sunday's 33-27 loss to the Bengals.</t>
         </is>
       </c>
     </row>
@@ -64290,7 +64294,7 @@
       </c>
       <c r="F755" s="4" t="inlineStr">
         <is>
-          <t>Dike recorded one catch for seven yards, three kick returns for 62 yards and one punt return for -5 yards in Sunday's 23-10 loss to the Jets.</t>
+          <t>Dike recorded one catch for seven yards, three kickoff returns for 62 yards and one punt return for minus-5 yards in Sunday's 23-10 loss to the Jets.</t>
         </is>
       </c>
     </row>
@@ -64322,7 +64326,7 @@
       </c>
       <c r="F756" s="5" t="inlineStr">
         <is>
-          <t>Slye made his only field-goal try and his only extra-point attempt during Sunday's 23-10 loss versus the Jets.</t>
+          <t>Slye made his only field-goal try and his sole extra-point attempt during Sunday's 23-10 loss versus the Jets.</t>
         </is>
       </c>
     </row>
@@ -65138,7 +65142,7 @@
       </c>
       <c r="F782" s="5" t="inlineStr">
         <is>
-          <t>Lane caught his only target for four yards while returning four punts for 53 yards and three kicks for 95 yards in Sunday's 24-22 loss to the Eagles.</t>
+          <t>Lane caught his only target for four yards while returning four punts for 53 yards and three kickoffs for 95 yards in Sunday's 24-22 loss to the Eagles.</t>
         </is>
       </c>
     </row>
@@ -65950,20 +65954,20 @@
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>64.40000000000001</v>
+        <v>68</v>
       </c>
       <c r="E5" s="17" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="G5" s="17" t="n">
         <v>14</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I5" s="9" t="n">
@@ -65988,20 +65992,20 @@
         </is>
       </c>
       <c r="D6" s="19" t="n">
-        <v>87.09999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="E6" s="19" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="F6" s="19" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="G6" s="19" t="n">
         <v>4</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Partly cloudy</t>
         </is>
       </c>
       <c r="I6" s="14" t="n">
@@ -66026,13 +66030,13 @@
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>92.8</v>
+        <v>92.3</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>4.4</v>
+        <v>6.9</v>
       </c>
       <c r="F7" s="17" t="n">
-        <v>5.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G7" s="17" t="n">
         <v>6</v>
@@ -66047,7 +66051,7 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>93°F · retractable roof — effect halved</t>
+          <t>92°F · retractable roof — effect halved</t>
         </is>
       </c>
     </row>
@@ -66068,20 +66072,20 @@
         </is>
       </c>
       <c r="D8" s="19" t="n">
-        <v>89.5</v>
+        <v>91</v>
       </c>
       <c r="E8" s="19" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="G8" s="19" t="n">
         <v>13</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>Mainly clear</t>
+          <t>Partly cloudy</t>
         </is>
       </c>
       <c r="I8" s="14" t="n">
@@ -66106,30 +66110,26 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>70.2</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="F9" s="17" t="n">
-        <v>23.9</v>
+        <v>6.3</v>
       </c>
       <c r="G9" s="17" t="n">
         <v>44</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Light drizzle</t>
+          <t>Rain showers</t>
         </is>
       </c>
       <c r="I9" s="9" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>Wind 9 mph (gusts 24)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -66148,10 +66148,10 @@
         </is>
       </c>
       <c r="D10" s="19" t="n">
-        <v>68</v>
+        <v>67.5</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="F10" s="19" t="n">
         <v>5.6</v>
@@ -66161,7 +66161,7 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Light drizzle</t>
+          <t>Drizzle</t>
         </is>
       </c>
       <c r="I10" s="14" t="n">
@@ -66186,13 +66186,13 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>84.7</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E11" s="17" t="n">
-        <v>6.7</v>
+        <v>4.7</v>
       </c>
       <c r="F11" s="17" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="G11" s="17" t="n">
         <v>20</v>
@@ -66224,13 +66224,13 @@
         </is>
       </c>
       <c r="D12" s="19" t="n">
-        <v>92.59999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>8.9</v>
+        <v>10.5</v>
       </c>
       <c r="G12" s="19" t="n">
         <v>3</v>
@@ -66241,13 +66241,9 @@
         </is>
       </c>
       <c r="I12" s="14" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>93°F</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -66266,13 +66262,13 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>62.8</v>
+        <v>54.4</v>
       </c>
       <c r="E13" s="17" t="n">
-        <v>7.4</v>
+        <v>3.9</v>
       </c>
       <c r="F13" s="17" t="n">
-        <v>23.5</v>
+        <v>11.4</v>
       </c>
       <c r="G13" s="17" t="n">
         <v>46</v>
@@ -66283,13 +66279,9 @@
         </is>
       </c>
       <c r="I13" s="9" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>Wind 7 mph (gusts 24)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -66308,20 +66300,20 @@
         </is>
       </c>
       <c r="D14" s="19" t="n">
-        <v>73.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="E14" s="19" t="n">
         <v>7.2</v>
       </c>
       <c r="F14" s="19" t="n">
-        <v>4.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G14" s="19" t="n">
         <v>23</v>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Mainly clear</t>
         </is>
       </c>
       <c r="I14" s="14" t="n">
@@ -66346,13 +66338,13 @@
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>78.8</v>
+        <v>78.3</v>
       </c>
       <c r="E15" s="17" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="F15" s="17" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="G15" s="17" t="n">
         <v>0</v>
@@ -66384,20 +66376,20 @@
         </is>
       </c>
       <c r="D16" s="19" t="n">
-        <v>74.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E16" s="19" t="n">
-        <v>8.4</v>
+        <v>10.1</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>7.4</v>
+        <v>10.1</v>
       </c>
       <c r="G16" s="19" t="n">
         <v>0</v>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>Mainly clear</t>
+          <t>Partly cloudy</t>
         </is>
       </c>
       <c r="I16" s="14" t="n">
@@ -66422,20 +66414,20 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>98.09999999999999</v>
+        <v>98.3</v>
       </c>
       <c r="E17" s="17" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="F17" s="17" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="G17" s="17" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Mainly clear</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
@@ -66464,20 +66456,20 @@
         </is>
       </c>
       <c r="D18" s="19" t="n">
-        <v>100.1</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="E18" s="19" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>6.9</v>
+        <v>8.9</v>
       </c>
       <c r="G18" s="19" t="n">
         <v>7</v>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Partly cloudy</t>
         </is>
       </c>
       <c r="I18" s="14" t="n">
@@ -66485,7 +66477,7 @@
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>100°F · retractable roof — effect halved</t>
+          <t>99°F · retractable roof — effect halved</t>
         </is>
       </c>
     </row>
@@ -66506,30 +66498,26 @@
         </is>
       </c>
       <c r="D19" s="17" t="n">
-        <v>68.90000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="E19" s="17" t="n">
-        <v>12.2</v>
+        <v>11.3</v>
       </c>
       <c r="F19" s="17" t="n">
-        <v>20.4</v>
+        <v>17</v>
       </c>
       <c r="G19" s="17" t="n">
         <v>36</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Rain showers</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>Wind 12 mph (gusts 20)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -66548,13 +66536,13 @@
         </is>
       </c>
       <c r="D20" s="19" t="n">
-        <v>74.2</v>
+        <v>74.7</v>
       </c>
       <c r="E20" s="19" t="n">
-        <v>10.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="G20" s="19" t="n">
         <v>0</v>
@@ -66586,30 +66574,26 @@
         </is>
       </c>
       <c r="D21" s="17" t="n">
-        <v>53.6</v>
+        <v>64.8</v>
       </c>
       <c r="E21" s="17" t="n">
-        <v>11.4</v>
+        <v>5.6</v>
       </c>
       <c r="F21" s="17" t="n">
-        <v>22.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G21" s="17" t="n">
         <v>8</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Mainly clear</t>
+          <t>Light drizzle</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>Wind 11 mph (gusts 23)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -66628,20 +66612,20 @@
         </is>
       </c>
       <c r="D22" s="19" t="n">
-        <v>74.09999999999999</v>
+        <v>60.5</v>
       </c>
       <c r="E22" s="19" t="n">
-        <v>6.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F22" s="19" t="n">
         <v>10.3</v>
       </c>
       <c r="G22" s="19" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>Partly cloudy</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I22" s="14" t="n">
@@ -66666,16 +66650,16 @@
         </is>
       </c>
       <c r="D23" s="17" t="n">
-        <v>74.5</v>
+        <v>66.3</v>
       </c>
       <c r="E23" s="17" t="n">
-        <v>3.3</v>
+        <v>6.9</v>
       </c>
       <c r="F23" s="17" t="n">
-        <v>5.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G23" s="17" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
@@ -66704,20 +66688,20 @@
         </is>
       </c>
       <c r="D24" s="19" t="n">
-        <v>79.2</v>
+        <v>63.3</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>7.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F24" s="19" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="G24" s="19" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>Mainly clear</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I24" s="14" t="n">
@@ -66742,26 +66726,30 @@
         </is>
       </c>
       <c r="D25" s="17" t="n">
-        <v>85.90000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>9.300000000000001</v>
+        <v>12</v>
       </c>
       <c r="F25" s="17" t="n">
-        <v>9.6</v>
+        <v>21.9</v>
       </c>
       <c r="G25" s="17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Overcast</t>
+          <t>Rain showers</t>
         </is>
       </c>
       <c r="I25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr"/>
+        <v>-0.68</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>Wind 12 mph (gusts 22) · canopy — wind damped</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -66780,20 +66768,20 @@
         </is>
       </c>
       <c r="D26" s="19" t="n">
-        <v>73</v>
+        <v>59.8</v>
       </c>
       <c r="E26" s="19" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>10.5</v>
+        <v>11.4</v>
       </c>
       <c r="G26" s="19" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>Mainly clear</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I26" s="14" t="n">
@@ -66818,20 +66806,20 @@
         </is>
       </c>
       <c r="D27" s="17" t="n">
-        <v>73.59999999999999</v>
+        <v>60.6</v>
       </c>
       <c r="E27" s="17" t="n">
-        <v>8.199999999999999</v>
+        <v>3.9</v>
       </c>
       <c r="F27" s="17" t="n">
-        <v>13.2</v>
+        <v>6.3</v>
       </c>
       <c r="G27" s="17" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Partly cloudy</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I27" s="9" t="n">
@@ -66860,20 +66848,20 @@
         </is>
       </c>
       <c r="D28" s="19" t="n">
-        <v>79.3</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="E28" s="19" t="n">
-        <v>1.3</v>
+        <v>11</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>2.2</v>
+        <v>15.2</v>
       </c>
       <c r="G28" s="19" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I28" s="14" t="n">
@@ -66898,20 +66886,20 @@
         </is>
       </c>
       <c r="D29" s="17" t="n">
-        <v>76</v>
+        <v>71.2</v>
       </c>
       <c r="E29" s="17" t="n">
-        <v>3.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F29" s="17" t="n">
-        <v>4.5</v>
+        <v>10.3</v>
       </c>
       <c r="G29" s="17" t="n">
         <v>12</v>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I29" s="9" t="n">
@@ -66936,30 +66924,26 @@
         </is>
       </c>
       <c r="D30" s="19" t="n">
-        <v>82.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>14.2</v>
+        <v>8.1</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>19</v>
+        <v>16.8</v>
       </c>
       <c r="G30" s="19" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>Thunderstorm, hail</t>
+          <t>Rain showers</t>
         </is>
       </c>
       <c r="I30" s="14" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>Wind 14 mph (gusts 19)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -66978,20 +66962,20 @@
         </is>
       </c>
       <c r="D31" s="17" t="n">
-        <v>76.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="E31" s="17" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="F31" s="17" t="n">
-        <v>10.1</v>
+        <v>7.6</v>
       </c>
       <c r="G31" s="17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I31" s="9" t="n">
@@ -67016,30 +67000,26 @@
         </is>
       </c>
       <c r="D32" s="19" t="n">
-        <v>88.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="E32" s="19" t="n">
-        <v>12.5</v>
+        <v>4.4</v>
       </c>
       <c r="F32" s="19" t="n">
-        <v>14.3</v>
+        <v>3.6</v>
       </c>
       <c r="G32" s="19" t="n">
         <v>49</v>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>Thunderstorm</t>
+          <t>Drizzle</t>
         </is>
       </c>
       <c r="I32" s="14" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>Wind 12 mph (gusts 14)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -67058,28 +67038,28 @@
         </is>
       </c>
       <c r="D33" s="17" t="n">
-        <v>74.59999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E33" s="17" t="n">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="F33" s="17" t="n">
-        <v>25.1</v>
+        <v>29.1</v>
       </c>
       <c r="G33" s="17" t="n">
         <v>13</v>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>Light drizzle</t>
+          <t>Drizzle</t>
         </is>
       </c>
       <c r="I33" s="9" t="n">
-        <v>-1.8</v>
+        <v>-3</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>Wind 8 mph (gusts 25)</t>
+          <t>Wind 7 mph (gusts 29)</t>
         </is>
       </c>
     </row>
@@ -67100,20 +67080,20 @@
         </is>
       </c>
       <c r="D34" s="19" t="n">
-        <v>90.5</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="E34" s="19" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>10.7</v>
+        <v>15.4</v>
       </c>
       <c r="G34" s="19" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>Overcast</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I34" s="14" t="n">
@@ -67142,20 +67122,20 @@
         </is>
       </c>
       <c r="D35" s="17" t="n">
-        <v>84.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="E35" s="17" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="F35" s="17" t="n">
-        <v>9.6</v>
+        <v>6.3</v>
       </c>
       <c r="G35" s="17" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Partly cloudy</t>
         </is>
       </c>
       <c r="I35" s="9" t="n">
@@ -67180,20 +67160,20 @@
         </is>
       </c>
       <c r="D36" s="19" t="n">
-        <v>73.8</v>
+        <v>59.9</v>
       </c>
       <c r="E36" s="19" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>11.6</v>
+        <v>7.8</v>
       </c>
       <c r="G36" s="19" t="n">
         <v>13</v>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>Overcast</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I36" s="14" t="n">
